--- a/indicadores/GSF-EPRIV-FOR_out.xlsx
+++ b/indicadores/GSF-EPRIV-FOR_out.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correlograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlograma" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -58,7 +59,7 @@
     <t xml:space="preserve">log</t>
   </si>
   <si>
-    <t xml:space="preserve">(1 0 1)</t>
+    <t xml:space="preserve">(0 1 2)</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -106,13 +107,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/11/2025</t>
+    <t xml:space="preserve">07/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">vcorvalan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -458,6 +459,63 @@
   </si>
   <si>
     <t xml:space="preserve">2030T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de las series incluidas en la hoja Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original | serie de datos brutos transformados, se importa directo desde base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_normal | serie original con 4 forecasts obtenidos del mejor modelo ARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_optimista | serie original con 4 forecasts, intervalo y límite optimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_pesimista | serie original con 4 forecasts, intervalo y límite pesimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_d16 | salida D16 del X13-ARIMA-SEATS con los factores estacionales de la serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_c17 | salida C17 del X13-ARIMA-SEATS con pesos del irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_d12 | salida D12 del X13-ARIMA-SEATS con el componente tendencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_1600 | tendencia HP de largo plazo con un lambda de 1.600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_200 | suavizado con filtro HP usando lambda de 200, sirve para determinar PG automáticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_ajustada | serie ajustada por estacionalidad usando el mejor modelo (LOG o NIV según el caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_filtrada | serie ajustada por estacionalidad y corregida por irregularidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final | serie f_filtrada con o sin suavizado 2x2 según el caso (es la vieja española)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final_fct_normal | a_original_fct ajustada por D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_tctl | tasas de cambio trimestral logarítmicas de la serie g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_var_interanual | variaciones interanuales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_var_trimestral | variaciones trimestrales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_irregular | g_final/d_d12 componente irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_dt | g_final/d_hp_1600 desvíos respecto de la tendencia</t>
   </si>
   <si>
     <t xml:space="preserve">Coeficientes de correlación de TCTL del ICA-SFE y serie específica</t>
@@ -1024,7 +1082,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.134051840054528</v>
+        <v>0.0684349357195195</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1082,7 +1140,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.000534286154551219</v>
+        <v>0.0000737807441455992</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1152,7 +1210,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.96252694963043</v>
+        <v>0.777269304951627</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1182,7 +1240,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.831321920478854</v>
+        <v>0.841567002084579</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1442,40 +1500,40 @@
         <v>74.903</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.0264320508178</v>
+        <v>1.02695157301084</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>72.1797627982077</v>
+        <v>72.1116082717147</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>71.7083745635824</v>
+        <v>71.4790567400052</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>72.1585550886513</v>
+        <v>71.7119052311341</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>72.9741437246837</v>
+        <v>72.9372270012671</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>72.9741437246837</v>
+        <v>72.9372270012671</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>72.9741437246837</v>
+        <v>72.9372270012671</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>72.9741437246837</v>
+        <v>72.9372270012671</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>1.0110055907041</v>
+        <v>1.01144917925615</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.01765162254485</v>
+        <v>1.0203999650774</v>
       </c>
     </row>
     <row r="3">
@@ -1495,44 +1553,44 @@
         <v>64.085</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.979179846756153</v>
+        <v>0.98061921515686</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>71.9329875243425</v>
+        <v>71.2840631052938</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>72.2474058586375</v>
+        <v>72.0565050056373</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>72.6525565968329</v>
+        <v>72.2640352054344</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>65.447629679371</v>
+        <v>65.3515646129257</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>71.9329875243425</v>
+        <v>71.2840631052938</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>71.9329875243425</v>
+        <v>71.2840631052938</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>71.9329875243425</v>
+        <v>71.2840631052938</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>-0.014370226063588</v>
+        <v>-0.0229263835501995</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>-0.0142674671767209</v>
+        <v>-0.0226655709840001</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.995648032887019</v>
+        <v>0.989280053198762</v>
       </c>
     </row>
     <row r="4">
@@ -1540,56 +1598,56 @@
         <v>54</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>70.261</v>
+        <v>69.046</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70.261</v>
+        <v>69.046</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>70.261</v>
+        <v>69.046</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>70.261</v>
+        <v>69.046</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.959832952764976</v>
+        <v>0.957106122496083</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>73.0254123955006</v>
+        <v>72.2321515893076</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>72.7872282594182</v>
+        <v>72.6348646276828</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>73.1506360481947</v>
+        <v>72.8222917885853</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>73.2012792409348</v>
+        <v>72.1403806507178</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>73.2012792409348</v>
+        <v>72.1403806507178</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>73.2012792409348</v>
+        <v>72.1403806507178</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>73.2012792409348</v>
+        <v>72.1403806507178</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.0174779399931526</v>
+        <v>0.0119411684406761</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0176315729436807</v>
+        <v>0.0120127488266091</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>1.00240829650481</v>
+        <v>0.998729500138504</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>1.00568851145205</v>
+        <v>0.993192195242607</v>
       </c>
     </row>
     <row r="5">
@@ -1609,44 +1667,44 @@
         <v>76.437</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.03349446210488</v>
+        <v>1.0343346955722</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>72.7294190836446</v>
+        <v>72.4342922425735</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>73.3284363601914</v>
+        <v>73.2145641863671</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>73.6532735405544</v>
+        <v>73.3879017289369</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>73.9597576984821</v>
+        <v>73.8996770844225</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>73.9597576984821</v>
+        <v>73.8996770844225</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>73.9597576984821</v>
+        <v>73.8996770844225</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>73.9597576984821</v>
+        <v>73.8996770844225</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0103082336142298</v>
+        <v>0.0240945062986562</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.0103615464840554</v>
+        <v>0.0243871243516529</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>1.01691665670287</v>
+        <v>1.02023053993462</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.00860950225625</v>
+        <v>1.00935760399135</v>
       </c>
     </row>
     <row r="6">
@@ -1666,46 +1724,46 @@
         <v>71.583</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.02630565811461</v>
+        <v>1.02658470552998</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>71.4936456121837</v>
+        <v>71.4921596347977</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>73.8718835370873</v>
+        <v>73.7957232094302</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>74.1612023876934</v>
+        <v>73.9586822191497</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>69.7482269867854</v>
+        <v>69.7292679448647</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>69.7482269867854</v>
+        <v>69.7292679448647</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>69.7482269867854</v>
+        <v>69.7292679448647</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>69.7482269867854</v>
+        <v>69.7292679448647</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>-0.0586291295637497</v>
+        <v>-0.0580883155623013</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.0442062979192881</v>
+        <v>-0.0439824653101593</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>-0.0569435439319064</v>
+        <v>-0.056433387858969</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>0.975586380992987</v>
+        <v>0.975341468226189</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.944178267117941</v>
+        <v>0.944895786805625</v>
       </c>
     </row>
     <row r="7">
@@ -1725,46 +1783,46 @@
         <v>72.422</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.980377428091943</v>
+        <v>0.982023819624594</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>72.7411330488357</v>
+        <v>72.7337425304775</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>74.4188177420724</v>
+        <v>74.3788894201735</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>74.6766883241827</v>
+        <v>74.5350093286618</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>73.8715497978683</v>
+        <v>73.7477019933033</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>73.8715497978683</v>
+        <v>73.7477019933033</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>73.8715497978683</v>
+        <v>73.7477019933033</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>73.8715497978683</v>
+        <v>73.7477019933033</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0574357705577883</v>
+        <v>0.0560296925682447</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.0269495587524398</v>
+        <v>0.0345608650894447</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0591172419603452</v>
+        <v>0.0576290869942304</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>1.01554026864379</v>
+        <v>1.01394070245184</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.992646108056958</v>
+        <v>0.991513890140192</v>
       </c>
     </row>
     <row r="8">
@@ -1784,46 +1842,46 @@
         <v>73.236</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.965363524318229</v>
+        <v>0.962812907764574</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>76.8139663528921</v>
+        <v>76.8734434144886</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>74.9679096417695</v>
+        <v>74.9620690073577</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>75.1799322075889</v>
+        <v>75.0961120555399</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>75.8636494492804</v>
+        <v>76.0646221185763</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>75.8636494492804</v>
+        <v>76.0646221185763</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>75.8636494492804</v>
+        <v>76.0646221185763</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>75.8636494492804</v>
+        <v>76.0646221185763</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.0266098714006349</v>
+        <v>0.030933434705969</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.0363705420991711</v>
+        <v>0.054397293616435</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0269670753742546</v>
+        <v>0.0314168450358414</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.987628331816042</v>
+        <v>0.989478534328803</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.01194830977402</v>
+        <v>1.01470814674433</v>
       </c>
     </row>
     <row r="9">
@@ -1843,46 +1901,46 @@
         <v>82.639</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.02461576427968</v>
+        <v>1.02531260684506</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>79.8447888827886</v>
+        <v>79.9029985010319</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>75.5174878603361</v>
+        <v>75.542873667602</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>75.6471092028468</v>
+        <v>75.6172828611737</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>80.653648793015</v>
+        <v>80.5988334175315</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>80.653648793015</v>
+        <v>80.5988334175315</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>80.653648793015</v>
+        <v>80.5988334175315</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>80.653648793015</v>
+        <v>80.5988334175315</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0612264030741414</v>
+        <v>0.0579009056523437</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.0905072069303214</v>
+        <v>0.0906520379710996</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0631395850121481</v>
+        <v>0.0596099891469504</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>1.01013040326794</v>
+        <v>1.00870849567042</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1.06801286798864</v>
+        <v>1.06692834816129</v>
       </c>
     </row>
     <row r="10">
@@ -1902,46 +1960,46 @@
         <v>82.172</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.02422762869461</v>
+        <v>1.02390211539001</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>80.4140279789236</v>
+        <v>80.3342544749721</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>76.0664408593096</v>
+        <v>76.11960419322</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>76.0578130610999</v>
+        <v>76.0786567572683</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>80.2282595175929</v>
+        <v>80.2537652426865</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>80.2282595175929</v>
+        <v>80.2537652426865</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>80.2282595175929</v>
+        <v>80.2537652426865</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>80.2282595175929</v>
+        <v>80.2537652426865</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>-0.00528822999722195</v>
+        <v>-0.00429049585849143</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.150255181867105</v>
+        <v>0.150933712743745</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>-0.00527427192430918</v>
+        <v>-0.00428130483052314</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>0.997689850067213</v>
+        <v>0.998998070837756</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.05471294057232</v>
+        <v>1.05431138395009</v>
       </c>
     </row>
     <row r="11">
@@ -1961,46 +2019,46 @@
         <v>76.665</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.988077151514076</v>
+        <v>0.990382882794109</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>76.7591061211244</v>
+        <v>76.7108775752521</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>76.61686720081</v>
+        <v>76.6937213513691</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>76.4166702314424</v>
+        <v>76.4852765083104</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>77.5900949460502</v>
+        <v>77.4094558093629</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>77.5900949460502</v>
+        <v>77.4094558093629</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>77.5900949460502</v>
+        <v>77.4094558093629</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>77.5900949460502</v>
+        <v>77.4094558093629</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>-0.0334360392750644</v>
+        <v>-0.0360847386080561</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.0503379874709118</v>
+        <v>0.0496524463418817</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>-0.0328832332572816</v>
+        <v>-0.035441445329356</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.01082593150075</v>
+        <v>1.00910663853931</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.01270252596846</v>
+        <v>1.0093323735683</v>
       </c>
     </row>
     <row r="12">
@@ -2020,46 +2078,46 @@
         <v>71.122</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.971884944922866</v>
+        <v>0.969628302158772</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.987893350398442</v>
+        <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>75.1474720220126</v>
+        <v>75.1633878154438</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>77.1734665836191</v>
+        <v>77.2692697598625</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>76.749159395251</v>
+        <v>76.8630604212141</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>73.1794441014256</v>
+        <v>73.3497566455668</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>73.2032703258663</v>
+        <v>73.3497566455668</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>73.2032703258663</v>
+        <v>73.3497566455668</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>73.2032703258663</v>
+        <v>73.3497566455668</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.0581996800422066</v>
+        <v>-0.053869754345424</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.0350679033071402</v>
+        <v>-0.0356915659000763</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.0565384618131244</v>
+        <v>-0.0524444865468889</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.974128182308291</v>
+        <v>0.975870816595837</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.94855490580495</v>
+        <v>0.949274619438274</v>
       </c>
     </row>
     <row r="13">
@@ -2079,46 +2137,46 @@
         <v>79.78</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.01136855970414</v>
+        <v>1.01150604590125</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>78.0367217902773</v>
+        <v>78.0508372049294</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>77.7415469738591</v>
+        <v>77.8507413705496</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>77.0866263574755</v>
+        <v>77.2425476993985</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>78.8832115004034</v>
+        <v>78.8724895152912</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>78.8832115004034</v>
+        <v>78.8724895152912</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>78.8832115004034</v>
+        <v>78.8724895152912</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>78.8832115004034</v>
+        <v>78.8724895152912</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.0747283266609355</v>
+        <v>0.0725933048376261</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>-0.0219511121828502</v>
+        <v>-0.0214189688490556</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.0775913582720102</v>
+        <v>0.0752931314606924</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.01084732534512</v>
+        <v>1.01052714281853</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.0146853847265</v>
+        <v>1.01312444977085</v>
       </c>
     </row>
     <row r="14">
@@ -2138,46 +2196,46 @@
         <v>81.632</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1.01999205526515</v>
+        <v>1.01943730818394</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>78.5510226961659</v>
+        <v>78.7362295526816</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>78.3239349649914</v>
+        <v>78.4401784395836</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>77.4426874777186</v>
+        <v>77.6367110274043</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>80.0319959146932</v>
+        <v>80.0755469165848</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>80.0319959146932</v>
+        <v>80.0755469165848</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>80.0319959146932</v>
+        <v>80.0755469165848</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>80.0319959146932</v>
+        <v>80.0755469165848</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.0144580804361856</v>
+        <v>0.0151380338204363</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>-0.00244631510243232</v>
+        <v>-0.00222068491818173</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.0145631040171832</v>
+        <v>0.0152531942212926</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1.01885364655602</v>
+        <v>1.01701017906893</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.02180764986419</v>
+        <v>1.0208486073022</v>
       </c>
     </row>
     <row r="15">
@@ -2197,46 +2255,46 @@
         <v>71.358</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.999763842682889</v>
+        <v>1.00259035141128</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.427069641019802</v>
+        <v>0.254717985670919</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>75.9081936875637</v>
+        <v>76.3195136724585</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>78.9241706908063</v>
+        <v>79.0402618157079</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>77.8399420412979</v>
+        <v>78.0666727988522</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>71.37485569443</v>
+        <v>71.1736352734236</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>73.9721426582147</v>
+        <v>75.0087658921488</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>73.9721426582147</v>
+        <v>75.0087658921488</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>73.9721426582147</v>
+        <v>75.0087658921488</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.0787379318850894</v>
+        <v>-0.0653655402575035</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.0466290483385952</v>
+        <v>-0.0310128768134769</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.0757178824196487</v>
+        <v>-0.0632750099067581</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.974494834677297</v>
+        <v>0.982825522369875</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.937255874984208</v>
+        <v>0.948994400689625</v>
       </c>
     </row>
     <row r="16">
@@ -2256,46 +2314,46 @@
         <v>75.162</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.979245498243957</v>
+        <v>0.977209622970903</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>74.9403806778276</v>
+        <v>75.2224713594378</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>79.5468618231879</v>
+        <v>79.6546944529643</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>78.3139358757155</v>
+        <v>78.5657495868083</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>76.7550120320033</v>
+        <v>76.9149200265683</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>76.7550120320033</v>
+        <v>76.9149200265683</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>76.7550120320033</v>
+        <v>76.9149200265683</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>76.7550120320033</v>
+        <v>76.9149200265683</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0369301159195121</v>
+        <v>0.0250948909748593</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.0485188939008654</v>
+        <v>0.0486049789943925</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0376205051494427</v>
+        <v>0.0254124182920203</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1.02421433328417</v>
+        <v>1.02249924306586</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>0.964903080684815</v>
+        <v>0.965604357091424</v>
       </c>
     </row>
     <row r="17">
@@ -2315,46 +2373,46 @@
         <v>75.163</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.997690468771758</v>
+        <v>0.997104270936833</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>76.8207492086171</v>
+        <v>76.8807130606639</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>80.1935210164997</v>
+        <v>80.284659620442</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>78.8808758115586</v>
+        <v>79.1519684298054</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>75.3369931382947</v>
+        <v>75.3812837742439</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>75.3369931382947</v>
+        <v>75.3812837742439</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>75.3369931382947</v>
+        <v>75.3812837742439</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>75.3369931382947</v>
+        <v>75.3812837742439</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.0186473967777903</v>
+        <v>-0.0201408578483848</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>-0.0449552990383827</v>
+        <v>-0.0442639222180308</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>-0.0184746097507916</v>
+        <v>-0.0199393856457846</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.980685477743871</v>
+        <v>0.980496678208007</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>0.93943989718065</v>
+        <v>0.93892512131982</v>
       </c>
     </row>
     <row r="18">
@@ -2374,46 +2432,46 @@
         <v>81.025</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.01337072941122</v>
+        <v>1.01284566859542</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>79.127057274967</v>
+        <v>79.0447919513544</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>80.8639160189857</v>
+        <v>80.929628228214</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>79.5491740601954</v>
+        <v>79.8351022185751</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>79.9559308833367</v>
+        <v>79.9973801658872</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>79.9559308833367</v>
+        <v>79.9973801658872</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>79.9559308833367</v>
+        <v>79.9973801658872</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>79.9559308833367</v>
+        <v>79.9973801658872</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.0595043280283741</v>
+        <v>0.0594348678162445</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>-0.000950432767384268</v>
+        <v>-0.000976162557828286</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.0613103543509237</v>
+        <v>0.061236638068779</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>1.01047522348126</v>
+        <v>1.01205124576859</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>0.988771442438729</v>
+        <v>0.988480756890443</v>
       </c>
     </row>
     <row r="19">
@@ -2433,46 +2491,46 @@
         <v>81.906</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.0111808239812</v>
+        <v>1.01502277348035</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>81.3820389665597</v>
+        <v>81.269802846093</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>81.5547792489662</v>
+        <v>81.5860065764495</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>80.3095234196279</v>
+        <v>80.6060704205712</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>81.0003493514854</v>
+        <v>80.6937559825948</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>81.0003493514854</v>
+        <v>80.6937559825948</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>81.0003493514854</v>
+        <v>80.6937559825948</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>81.0003493514854</v>
+        <v>80.6937559825948</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.0129778487101416</v>
+        <v>0.00866731286914931</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0950115332706294</v>
+        <v>0.0757910095284084</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0130624264718093</v>
+        <v>0.00870498277898091</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.995309903512848</v>
+        <v>0.992911920008111</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.993201748535321</v>
+        <v>0.989063681000019</v>
       </c>
     </row>
     <row r="20">
@@ -2492,46 +2550,46 @@
         <v>79.225</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.988493156479398</v>
+        <v>0.985700625346588</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>78.539417807891</v>
+        <v>78.6352049596182</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>82.2622756340516</v>
+        <v>82.2496183102784</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>81.1546504719739</v>
+        <v>81.4566038929839</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>80.1472417696512</v>
+        <v>80.3743022605299</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>80.1472417696512</v>
+        <v>80.3743022605299</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>80.1472417696512</v>
+        <v>80.3743022605299</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>80.1472417696512</v>
+        <v>80.3743022605299</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.0105880025353499</v>
+        <v>-0.00396669761124303</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0441955469466087</v>
+        <v>0.0449767383593014</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.0105321469433697</v>
+        <v>-0.00395884065842533</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>1.02047155436895</v>
+        <v>1.0221160140907</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>0.974289139850577</v>
+        <v>0.9771996990591</v>
       </c>
     </row>
     <row r="21">
@@ -2551,46 +2609,46 @@
         <v>72.614</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.984900796038441</v>
+        <v>0.983783088442959</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.948848536934184</v>
+        <v>0.90040322044932</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>75.9668428778714</v>
+        <v>76.1475381170043</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>82.9822235831665</v>
+        <v>82.9157294182097</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>82.0807359290104</v>
+        <v>82.3788719208138</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>73.7272223680545</v>
+        <v>73.8109862357227</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>73.8417822338438</v>
+        <v>74.0436992783514</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>73.8417822338438</v>
+        <v>74.0436992783514</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>73.8417822338438</v>
+        <v>74.0436992783514</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0819407387777668</v>
+        <v>-0.0820390517711422</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>-0.0198469681648457</v>
+        <v>-0.0177442520068822</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.0786734439836339</v>
+        <v>-0.0787640179028626</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>0.972026471503575</v>
+        <v>0.972371544889341</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>0.88985060950841</v>
+        <v>0.892999432048537</v>
       </c>
     </row>
     <row r="22">
@@ -2610,46 +2668,46 @@
         <v>81.115</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.00688357212958</v>
+        <v>1.0062961818815</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>80.8519652802206</v>
+        <v>81.0764566792485</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>83.7091196090699</v>
+        <v>83.5784338162212</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>83.0789234590028</v>
+        <v>83.359632280899</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>80.5604562883473</v>
+        <v>80.6074806408756</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>80.5604562883473</v>
+        <v>80.6074806408756</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>80.5604562883473</v>
+        <v>80.6074806408756</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>80.5604562883473</v>
+        <v>80.6074806408756</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.0870831860195895</v>
+        <v>0.0849360074293449</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>0.00756073249766342</v>
+        <v>0.00762650568960144</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.0909874308454071</v>
+        <v>0.088647399123712</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>0.99639453424709</v>
+        <v>0.994215632286099</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>0.962385659586109</v>
+        <v>0.964453112607034</v>
       </c>
     </row>
     <row r="23">
@@ -2669,46 +2727,46 @@
         <v>93.59</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.01916382324053</v>
+        <v>1.02578151049948</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.574942121773812</v>
+        <v>0.85555034628409</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>87.8395376569388</v>
+        <v>88.3358927822563</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>84.431747448678</v>
+        <v>84.2262804014535</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>84.0991619617407</v>
+        <v>84.3439668868653</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>91.8301826122728</v>
+        <v>91.2377529152661</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>90.1339275348045</v>
+        <v>90.8185802239208</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>90.1339275348045</v>
+        <v>90.8185802239208</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>90.1339275348045</v>
+        <v>90.8185802239208</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.112288735600001</v>
+        <v>0.119272435563184</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.112759738154779</v>
+        <v>0.125472214275289</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.118835861755688</v>
+        <v>0.126676823315419</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>1.02612024082853</v>
+        <v>1.02810508122428</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.06753597146136</v>
+        <v>1.07826891786086</v>
       </c>
     </row>
     <row r="24">
@@ -2728,46 +2786,46 @@
         <v>88.207</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.997836689589435</v>
+        <v>0.992138316168067</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>90.5394060734804</v>
+        <v>91.0216231767187</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>85.1369229243311</v>
+        <v>84.8459612253122</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>85.0788080011605</v>
+        <v>85.2631968941385</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>88.3982328173293</v>
+        <v>88.9059504733994</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>88.3982328173293</v>
+        <v>88.9059504733994</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>88.3982328173293</v>
+        <v>88.9059504733994</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>88.3982328173293</v>
+        <v>88.9059504733994</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.0194446692613263</v>
+        <v>-0.0212848179517566</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0.102947910189997</v>
+        <v>0.106148955237142</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.0192568410691413</v>
+        <v>-0.0210598948563799</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>0.976350924431585</v>
+        <v>0.976756372502699</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.03830664511914</v>
+        <v>1.04785129650786</v>
       </c>
     </row>
     <row r="25">
@@ -2787,46 +2845,46 @@
         <v>89.865</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.975725416907992</v>
+        <v>0.974843360716823</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>90.3314088104842</v>
+        <v>90.5880883969661</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>85.8150257209236</v>
+        <v>85.4282885265923</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>85.9853919690636</v>
+        <v>86.0810165248297</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>92.1007062466161</v>
+        <v>92.1840406585119</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>92.1007062466161</v>
+        <v>92.1840406585119</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>92.1007062466161</v>
+        <v>92.1840406585119</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>92.1007062466161</v>
+        <v>92.1840406585119</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.0410306328008636</v>
+        <v>0.0362079460310631</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.247270900842419</v>
+        <v>0.244995071247936</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.0418840208823836</v>
+        <v>0.0368714373746373</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.01958673577032</v>
+        <v>1.01761768340394</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.07324685243507</v>
+        <v>1.07908097245582</v>
       </c>
     </row>
     <row r="26">
@@ -2846,46 +2904,46 @@
         <v>88.789</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.00135211540766</v>
+        <v>0.999866285621895</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>90.0643277857192</v>
+        <v>89.7906828466592</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>86.4584738420328</v>
+        <v>85.9666120373687</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>86.8030413813327</v>
+        <v>86.7793337689462</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>88.66910913136</v>
+        <v>88.8008739536359</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>88.66910913136</v>
+        <v>88.8008739536359</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>88.66910913136</v>
+        <v>88.8008739536359</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>88.66910913136</v>
+        <v>88.8008739536359</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>-0.0379710451619749</v>
+        <v>-0.0373905289999283</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.100653015345267</v>
+        <v>0.101645569959738</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>-0.0372591835079675</v>
+        <v>-0.0367001346513836</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.984508643003713</v>
+        <v>0.988976485514498</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.02556875215455</v>
+        <v>1.03296933366451</v>
       </c>
     </row>
     <row r="27">
@@ -2905,46 +2963,46 @@
         <v>91.875</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.02462379378924</v>
+        <v>1.03546715246575</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>88.8664015348084</v>
+        <v>88.6021913607896</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>87.0636138415648</v>
+        <v>86.4585038347988</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>87.5464603252379</v>
+        <v>87.3705717371636</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>89.667056881658</v>
+        <v>88.7280680813667</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>89.667056881658</v>
+        <v>88.7280680813667</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>89.667056881658</v>
+        <v>88.7280680813667</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>89.667056881658</v>
+        <v>88.7280680813667</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.0111918764358375</v>
+        <v>-0.000820214163575699</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>-0.00517974380919128</v>
+        <v>-0.0230185512413844</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0112547397856402</v>
+        <v>-0.000819877879886466</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>1.00900965193843</v>
+        <v>1.00142069534222</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.02990276793278</v>
+        <v>1.02625032987969</v>
       </c>
     </row>
     <row r="28">
@@ -2964,46 +3022,46 @@
         <v>87.797</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.00160152641198</v>
+        <v>0.992538901177367</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>88.1533903828678</v>
+        <v>88.3289590738522</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>87.6281739204813</v>
+        <v>86.9033074097377</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>88.2396832267995</v>
+        <v>87.8772612410812</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>87.6566156149079</v>
+        <v>88.4569863164594</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>87.6566156149079</v>
+        <v>88.4569863164594</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>87.6566156149079</v>
+        <v>88.4569863164594</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>87.6566156149079</v>
+        <v>88.4569863164594</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.0226763566080782</v>
+        <v>-0.00305987406597334</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.00838950258150339</v>
+        <v>-0.00504987747782182</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.0224211804944532</v>
+        <v>-0.00305519742251958</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>0.99436465499736</v>
+        <v>1.00144943678664</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.00032457248798</v>
+        <v>1.01787824828572</v>
       </c>
     </row>
     <row r="29">
@@ -3023,46 +3081,46 @@
         <v>83.817</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.973438930222905</v>
+        <v>0.972430425249531</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>85.1761294512765</v>
+        <v>85.6674868541571</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>88.1515094316443</v>
+        <v>87.3017847306945</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>88.9173474948201</v>
+        <v>88.3287205740192</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>86.1040147436953</v>
+        <v>86.1933129853399</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>86.1040147436953</v>
+        <v>86.1933129853399</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>86.1040147436953</v>
+        <v>86.1933129853399</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>86.1040147436953</v>
+        <v>86.1933129853399</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>-0.0178710469630045</v>
+        <v>-0.0259238044559657</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>-0.0651101576448674</v>
+        <v>-0.064986603216539</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>-0.0177123068272852</v>
+        <v>-0.025590667570576</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>1.01089372454931</v>
+        <v>1.00613798945775</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.976773004782899</v>
+        <v>0.987302988721549</v>
       </c>
     </row>
     <row r="30">
@@ -3082,46 +3140,46 @@
         <v>81.62</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.998899956101907</v>
+        <v>0.996747424258214</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>82.6294489973381</v>
+        <v>82.3081694823798</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>88.6329935039746</v>
+        <v>87.655668815495</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>89.6111752000427</v>
+        <v>88.7571666546746</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>81.7098844598139</v>
+        <v>81.8863415280377</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>81.7098844598139</v>
+        <v>81.8863415280377</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>81.7098844598139</v>
+        <v>81.8863415280377</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>81.7098844598139</v>
+        <v>81.8863415280377</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>-0.0523810598251019</v>
+        <v>-0.0512603922424904</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>-0.0784853342919717</v>
+        <v>-0.0778655898049874</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>-0.0510328153334237</v>
+        <v>-0.0499687424479754</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.988871225105787</v>
+        <v>0.994875017182439</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.921890158839662</v>
+        <v>0.934181926104504</v>
       </c>
     </row>
     <row r="31">
@@ -3141,46 +3199,46 @@
         <v>85.937</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1.02535719135176</v>
+        <v>1.03981268241418</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>84.123522095996</v>
+        <v>83.5398843396373</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>89.0707195822133</v>
+        <v>87.9659998871245</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>90.3388217494546</v>
+        <v>89.1841393638013</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>83.8117689375218</v>
+        <v>82.6466165044998</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>83.8117689375218</v>
+        <v>82.6466165044998</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>83.8117689375218</v>
+        <v>82.6466165044998</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>83.8117689375218</v>
+        <v>82.6466165044998</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.025398459040909</v>
+        <v>0.00924167895254638</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0653003248658424</v>
+        <v>-0.0685403357513658</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0257237480092338</v>
+        <v>0.00928451512517259</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.99629410240196</v>
+        <v>0.989307289060806</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.94095758213969</v>
+        <v>0.939529097725822</v>
       </c>
     </row>
     <row r="32">
@@ -3200,46 +3258,46 @@
         <v>94.097</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.00073500391742</v>
+        <v>0.989402097660021</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>88.0788222659482</v>
+        <v>88.6831179111276</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>89.4584541679485</v>
+        <v>88.230212339013</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>91.0784360963421</v>
+        <v>89.5968244565196</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>94.0278891331404</v>
+        <v>95.1049125755277</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>88.0788222659482</v>
+        <v>88.6831179111276</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>88.0788222659482</v>
+        <v>88.6831179111276</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>88.0788222659482</v>
+        <v>88.6831179111276</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.0496586827301188</v>
+        <v>0.0704956574597109</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.00481659767581144</v>
+        <v>0.00255640175055483</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.0509123406237537</v>
+        <v>0.0730399097015557</v>
       </c>
       <c r="R32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.984577959513919</v>
+        <v>1.00513322545767</v>
       </c>
     </row>
     <row r="33">
@@ -3259,46 +3317,46 @@
         <v>88.379</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.976416751205388</v>
+        <v>0.974892283880907</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>1</v>
+        <v>0.399989714514293</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>91.6647576758223</v>
+        <v>93.3154597281752</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>89.7866769186157</v>
+        <v>88.4424159499768</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>91.7755319299317</v>
+        <v>89.9497200736535</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>90.5136048627761</v>
+        <v>90.6551436105083</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>90.5136048627761</v>
+        <v>92.2513606437518</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>90.5136048627761</v>
+        <v>92.2513606437518</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>90.5136048627761</v>
+        <v>92.2513606437518</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.0272680482437327</v>
+        <v>0.0394474890834582</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.0512123636999591</v>
+        <v>0.0702844275105463</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.0276432238101025</v>
+        <v>0.0402358737116133</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.987441707781333</v>
+        <v>0.988596754626478</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>1.00809616714982</v>
+        <v>1.04306694534362</v>
       </c>
     </row>
     <row r="34">
@@ -3318,46 +3376,46 @@
         <v>95.958</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.00122140983442</v>
+        <v>0.998747638099274</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>94.8266873489085</v>
+        <v>95.9204055824935</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>90.0450052217115</v>
+        <v>88.5970035648148</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>92.3606248702981</v>
+        <v>90.1927558233003</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>95.8409389346452</v>
+        <v>96.0783248335071</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>95.8409389346452</v>
+        <v>96.0783248335071</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>95.8409389346452</v>
+        <v>96.0783248335071</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>95.8409389346452</v>
+        <v>96.0783248335071</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>0.0571897618336445</v>
+        <v>0.0406467101604059</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0.172941799737596</v>
+        <v>0.173313192904216</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>0.0588567219253464</v>
+        <v>0.0414840947932882</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.01069584537953</v>
+        <v>1.00164635720684</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>1.06436707620442</v>
+        <v>1.08444214778911</v>
       </c>
     </row>
     <row r="35">
@@ -3377,46 +3435,46 @@
         <v>99.608</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1.0196624560549</v>
+        <v>1.0355858764581</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>98.9887527822748</v>
+        <v>95.5363684344069</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>90.2235107946976</v>
+        <v>88.6907486187593</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>92.75792090218</v>
+        <v>90.2873695164072</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>97.6872291497187</v>
+        <v>96.1851665461857</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>97.6872291497187</v>
+        <v>96.1851665461857</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>97.6872291497187</v>
+        <v>96.1851665461857</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>97.6872291497187</v>
+        <v>96.1851665461857</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.0190809043416768</v>
+        <v>0.00111140937792971</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.165555033476749</v>
+        <v>0.163812514223722</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.0192641081733615</v>
+        <v>0.00111202722220383</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>0.986851802897055</v>
+        <v>1.00679111130568</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>1.08272476086643</v>
+        <v>1.08450056002618</v>
       </c>
     </row>
     <row r="36">
@@ -3424,58 +3482,58 @@
         <v>86</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>102.126433149024</v>
+        <v>90.0095</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>102.126433149024</v>
+        <v>90.0095</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>102.126433149024</v>
+        <v>90.0095</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>102.126433149024</v>
+        <v>90.0095</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.997842727895959</v>
+        <v>0.986450593368895</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>100.540222477229</v>
+        <v>91.5034040195123</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>90.3158878136064</v>
+        <v>88.7251003728356</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>92.9090275806381</v>
+        <v>90.224426808973</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>102.347223960199</v>
+        <v>91.2458268108516</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>102.347223960199</v>
+        <v>91.2458268108516</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>102.347223960199</v>
+        <v>91.2458268108516</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>102.347223960199</v>
+        <v>91.2458268108516</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0466003531739206</v>
+        <v>-0.0527178940388836</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0.161995827455194</v>
+        <v>0.0288973703235402</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.0477032141359921</v>
+        <v>-0.051352406121398</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.01797292107027</v>
+        <v>0.997185053261999</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>1.13321394981383</v>
+        <v>1.02841052224707</v>
       </c>
     </row>
     <row r="37">
@@ -3483,58 +3541,58 @@
         <v>87</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>96.7086807210438</v>
+        <v>86.652</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>96.7086807210438</v>
+        <v>86.652</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>96.7086807210438</v>
+        <v>86.652</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>96.7086807210438</v>
+        <v>86.652</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.982910092057207</v>
+        <v>0.980719123893401</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>100.085780896163</v>
+        <v>89.1069758926866</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>90.3204952784421</v>
+        <v>88.7061920992738</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>92.7801990019705</v>
+        <v>90.0242823421451</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>98.3901594891908</v>
+        <v>88.3555728535162</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>98.3901594891908</v>
+        <v>88.3555728535162</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>98.3901594891908</v>
+        <v>88.3555728535162</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>98.3901594891908</v>
+        <v>88.3555728535162</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>-0.0394303948659258</v>
+        <v>-0.032187984054237</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.0870206709627357</v>
+        <v>-0.042230139079249</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>-0.0386631343567025</v>
+        <v>-0.031675464603184</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>0.983058318656359</v>
+        <v>0.991567405002328</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>1.08934477369584</v>
+        <v>0.996047409572432</v>
       </c>
     </row>
     <row r="38">
@@ -3542,58 +3600,58 @@
         <v>88</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>99.5878818737883</v>
+        <v>91.424</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>99.5878818737883</v>
+        <v>91.424</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>99.5878818737883</v>
+        <v>91.424</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>99.5878818737883</v>
+        <v>91.424</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.00598991163399</v>
+        <v>1.0035376322818</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>98.1019256952345</v>
+        <v>91.0751233106311</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>90.2432117743005</v>
+        <v>88.6417325243275</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>92.3848802443734</v>
+        <v>89.7123977570804</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>98.9949111040603</v>
+        <v>91.1017156298605</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>98.9949111040603</v>
+        <v>91.1017156298605</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>98.9949111040603</v>
+        <v>91.1017156298605</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>98.9949111040603</v>
+        <v>91.1017156298605</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.00612765195791679</v>
+        <v>0.0306073626862079</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.0329084022388999</v>
+        <v>-0.0517974185360799</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.00614646442295874</v>
+        <v>0.0310805836876529</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00910262874554</v>
+        <v>1.00029198224787</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.09697903208108</v>
+        <v>1.02775197455508</v>
       </c>
     </row>
     <row r="39">
@@ -3613,46 +3671,46 @@
         <v>95.267</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1.01081613169901</v>
+        <v>1.02616195057695</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>93.6511887419888</v>
+        <v>91.5257464660411</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>90.0949594264091</v>
+        <v>88.5392112372219</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>91.764566188479</v>
+        <v>89.3058911474925</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>94.2476054867391</v>
+        <v>92.838172324005</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>94.2476054867391</v>
+        <v>92.838172324005</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>94.2476054867391</v>
+        <v>92.838172324005</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>94.2476054867391</v>
+        <v>92.838172324005</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>-0.0491430257949816</v>
+        <v>0.018881258444452</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>-0.035210576581182</v>
+        <v>-0.0347974052794668</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>-0.0479550470259125</v>
+        <v>0.0190606365877857</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00636849091573</v>
+        <v>1.01433941714369</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>1.04609188002046</v>
+        <v>1.04855431877821</v>
       </c>
     </row>
     <row r="40">
@@ -3672,46 +3730,46 @@
         <v>85.922</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.994513863673002</v>
+        <v>0.98442935075714</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>87.6469883177229</v>
+        <v>88.3558688997179</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>89.8921301720767</v>
+        <v>88.407655316623</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>90.9938018692177</v>
+        <v>88.828827196459</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>86.3959801250707</v>
+        <v>87.2810221819535</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>86.3959801250707</v>
+        <v>87.2810221819535</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>86.3959801250707</v>
+        <v>87.2810221819535</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>86.3959801250707</v>
+        <v>87.2810221819535</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>-0.0869842716317126</v>
+        <v>-0.0617248419316777</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>-0.155854191427135</v>
+        <v>-0.0434519009523253</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>-0.0833084864185019</v>
+        <v>-0.0598584612658799</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.985726740682553</v>
+        <v>0.987835027472998</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.961107273347362</v>
+        <v>0.987256384861304</v>
       </c>
     </row>
     <row r="41">
@@ -3731,46 +3789,46 @@
         <v>84.925</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.989681896964369</v>
+        <v>0.987266560755259</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>85.1124429912194</v>
+        <v>85.727283879576</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>89.6537113523994</v>
+        <v>88.2587786918761</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>90.1595475180116</v>
+        <v>88.3229319929403</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>85.8104005544496</v>
+        <v>86.0203347057884</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>85.8104005544496</v>
+        <v>86.0203347057884</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>85.8104005544496</v>
+        <v>86.0203347057884</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>85.8104005544496</v>
+        <v>86.0203347057884</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>-0.00680093066656087</v>
+        <v>-0.0145493346109219</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>-0.127855864855298</v>
+        <v>-0.0264300040428617</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>-0.00677785667543174</v>
+        <v>-0.014444004488592</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>1.00820041745603</v>
+        <v>1.00341840792045</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.957131604035408</v>
+        <v>0.974637718544663</v>
       </c>
     </row>
     <row r="42">
@@ -3790,46 +3848,46 @@
         <v>86.89</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.01242439949166</v>
+        <v>1.01025731770306</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>86.6184856947868</v>
+        <v>86.3529540357628</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>89.3965052146945</v>
+        <v>88.1035911466176</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>89.3257742575618</v>
+        <v>87.8221926008238</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>85.8236921627211</v>
+        <v>86.0077907651832</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>85.8236921627211</v>
+        <v>86.0077907651832</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>85.8236921627211</v>
+        <v>86.0077907651832</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>85.8236921627211</v>
+        <v>86.0077907651832</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.00015488307815392</v>
+        <v>-0.000145835927620885</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>-0.133049454708778</v>
+        <v>-0.0559146974286795</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.000154895073157135</v>
+        <v>-0.000145825294078916</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.990824204259743</v>
+        <v>0.996002878252009</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.960034085858358</v>
+        <v>0.9762120890402</v>
       </c>
     </row>
     <row r="43">
@@ -3849,46 +3907,46 @@
         <v>89.474</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1.00223807525435</v>
+        <v>1.01460383172613</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>88.4302359442732</v>
+        <v>88.0256253387488</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>89.13491193703</v>
+        <v>87.951703436992</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>88.5347074757516</v>
+        <v>87.3490830975615</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>89.2741976274381</v>
+        <v>88.186144386799</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>89.2741976274381</v>
+        <v>88.186144386799</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>89.2741976274381</v>
+        <v>88.186144386799</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>89.2741976274381</v>
+        <v>88.186144386799</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0394174049798912</v>
+        <v>0.0250119751088533</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>-0.0527695938121289</v>
+        <v>-0.0501089995715388</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0402045796185841</v>
+        <v>0.0253273988581231</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.00954381354016</v>
+        <v>1.0018235490794</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.00156263900846</v>
+        <v>1.00266556462974</v>
       </c>
     </row>
     <row r="44">
@@ -3908,46 +3966,46 @@
         <v>87.112</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.987934023698537</v>
+        <v>0.981020216346337</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>88.4861767171871</v>
+        <v>88.562818479769</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>88.8810986893168</v>
+        <v>87.8114164439061</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>87.8110621499902</v>
+        <v>86.917005551427</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>88.1759286656391</v>
+        <v>88.7973545789256</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>88.1759286656391</v>
+        <v>88.7973545789256</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>88.1759286656391</v>
+        <v>88.7973545789256</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>88.1759286656391</v>
+        <v>88.7973545789256</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.0123784976480972</v>
+        <v>0.00690700122436927</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0206022148020268</v>
+        <v>0.0173729908182223</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.0123021991906589</v>
+        <v>0.0069309095706207</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>0.996493824650831</v>
+        <v>1.00264824565413</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.992066141912325</v>
+        <v>1.01122790378458</v>
       </c>
     </row>
     <row r="45">
@@ -3967,46 +4025,46 @@
         <v>85.925</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.99869996002545</v>
+        <v>0.996006735620869</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>85.6365446409733</v>
+        <v>86.099886742666</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>88.6473196950221</v>
+        <v>87.6911775738597</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>87.1832507084453</v>
+        <v>86.5435473371404</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>86.0368513460343</v>
+        <v>86.2694969090123</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>86.0368513460343</v>
+        <v>86.2694969090123</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>86.0368513460343</v>
+        <v>86.2694969090123</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>86.0368513460343</v>
+        <v>86.2694969090123</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.0245582996452832</v>
+        <v>-0.0288807772917577</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.00263896672339836</v>
+        <v>0.00289655003175771</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.0242591980824627</v>
+        <v>-0.0284677137275128</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.00467448455258</v>
+        <v>1.00196992322247</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.970552202165065</v>
+        <v>0.983787643133769</v>
       </c>
     </row>
     <row r="46">
@@ -4026,46 +4084,46 @@
         <v>83.698</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.01897197363442</v>
+        <v>1.01791667062343</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>82.3253675539267</v>
+        <v>82.1909154367643</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>88.4453884463484</v>
+        <v>87.6000504446875</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>86.6815099118625</v>
+        <v>86.2556975745588</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>82.1396487495824</v>
+        <v>82.2248052473083</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>82.1396487495824</v>
+        <v>82.2248052473083</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>82.1396487495824</v>
+        <v>82.2248052473083</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>82.1396487495824</v>
+        <v>82.2248052473083</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>-0.0463548762170408</v>
+        <v>-0.0480190579462322</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>-0.0429257157353915</v>
+        <v>-0.0439842191529269</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>-0.0452968993574344</v>
+        <v>-0.0468843775218709</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.997744087759795</v>
+        <v>1.00041233036965</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>0.928704709114471</v>
+        <v>0.938638788789588</v>
       </c>
     </row>
     <row r="47">
@@ -4085,46 +4143,46 @@
         <v>80.547</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.991728515622033</v>
+        <v>0.99939894372727</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>81.7850309226486</v>
+        <v>81.5213788697338</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>88.2854868927802</v>
+        <v>87.5462101238083</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>86.3303445241757</v>
+        <v>86.0790751313991</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>81.2188000356925</v>
+        <v>80.5954423962057</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>81.2188000356925</v>
+        <v>80.5954423962057</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>81.2188000356925</v>
+        <v>80.5954423962057</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>81.2188000356925</v>
+        <v>80.5954423962057</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>-0.0112740843760625</v>
+        <v>-0.0200149215774988</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>-0.0902320917558136</v>
+        <v>-0.08607590277787</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>-0.0112107700472072</v>
+        <v>-0.0198159526945909</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.993076595061856</v>
+        <v>0.988641795730569</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.919956415195739</v>
+        <v>0.920604584507167</v>
       </c>
     </row>
     <row r="48">
@@ -4144,46 +4202,46 @@
         <v>84.243</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.985534876299497</v>
+        <v>0.982137965699148</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>85.4906597851317</v>
+        <v>85.506714023453</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>88.1738558964913</v>
+        <v>87.5344721503927</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>86.1315500035073</v>
+        <v>86.0191444137416</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>85.4794711236573</v>
+        <v>85.775118101692</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>85.4794711236573</v>
+        <v>85.775118101692</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>85.4794711236573</v>
+        <v>85.775118101692</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>85.4794711236573</v>
+        <v>85.775118101692</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.0511294953938767</v>
+        <v>0.0622868636603341</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.030580426912278</v>
+        <v>-0.0340352084987769</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0524591730743673</v>
+        <v>0.0642676006420211</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.999869124165113</v>
+        <v>1.00313898249166</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.969442361962746</v>
+        <v>0.979901014931833</v>
       </c>
     </row>
     <row r="49">
@@ -4203,46 +4261,46 @@
         <v>92.858</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.00424054759712</v>
+        <v>1.00170494831643</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.17578165445933</v>
+        <v>0.181180439466808</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>88.3349705302088</v>
+        <v>88.5563801657016</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>88.1123196403698</v>
+        <v>87.5653078337815</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>86.0613640855371</v>
+        <v>86.053951663991</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>92.4658939754867</v>
+        <v>92.6999513739718</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>89.0611110878646</v>
+        <v>89.307114218178</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>89.0611110878646</v>
+        <v>89.307114218178</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>89.0611110878646</v>
+        <v>89.307114218178</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0410465322421412</v>
+        <v>0.0403521855848499</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0351507487142571</v>
+        <v>0.0352107919716915</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0419005863878825</v>
+        <v>0.0411773972995124</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.00822030678561</v>
+        <v>1.00847746995837</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.01076797718375</v>
+        <v>1.0198915121466</v>
       </c>
     </row>
     <row r="50">
@@ -4262,46 +4320,46 @@
         <v>89.564</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.02514027274609</v>
+        <v>1.0253423123696</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>88.4329976132345</v>
+        <v>88.355352578422</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>88.101018316821</v>
+        <v>87.6380888870352</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>86.092764111546</v>
+        <v>86.1603229929914</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>87.3675558175866</v>
+        <v>87.3503403882891</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>87.3675558175866</v>
+        <v>87.3503403882891</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>87.3675558175866</v>
+        <v>87.3503403882891</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>87.3675558175866</v>
+        <v>87.3503403882891</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0191987766960183</v>
+        <v>-0.0221542178015689</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.0636465719976773</v>
+        <v>0.0623356312680179</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.019015653966041</v>
+        <v>-0.0219106153750362</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.98795198823512</v>
+        <v>0.988625338920572</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.991674755715118</v>
+        <v>0.996716627411661</v>
       </c>
     </row>
     <row r="51">
@@ -4321,46 +4379,46 @@
         <v>86.82</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.982231304220211</v>
+        <v>0.985281164933762</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>87.691510376102</v>
+        <v>87.5310065894602</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>88.1406851129047</v>
+        <v>87.7532756522044</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>86.2137261578262</v>
+        <v>86.3313503243581</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>88.3905854221639</v>
+        <v>88.1169792846255</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>88.3905854221639</v>
+        <v>88.1169792846255</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>88.3905854221639</v>
+        <v>88.1169792846255</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>88.3905854221639</v>
+        <v>88.1169792846255</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0116414653803922</v>
+        <v>0.00873830837574197</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.0883020357764424</v>
+        <v>0.0933245933615463</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0117094909546656</v>
+        <v>0.00877659884241511</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00797198090287</v>
+        <v>1.00669445854671</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>1.00283524355341</v>
+        <v>1.00414461602394</v>
       </c>
     </row>
     <row r="52">
@@ -4380,46 +4438,46 @@
         <v>85.782</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.985677749212694</v>
+        <v>0.984957025946473</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>87.560074377082</v>
+        <v>87.5467132904612</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>88.2315948016188</v>
+        <v>87.9111486285279</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>86.4186002592004</v>
+        <v>86.5660756686827</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>87.0284431889814</v>
+        <v>87.0921245701757</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>87.0284431889814</v>
+        <v>87.0921245701757</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>87.0284431889814</v>
+        <v>87.0921245701757</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>87.0284431889814</v>
+        <v>87.0921245701757</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>-0.0155304657925685</v>
+        <v>-0.0116987802627558</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.0181209832602185</v>
+        <v>0.0153541784334501</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.0154104900049788</v>
+        <v>-0.0116306156063232</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>0.993928383548293</v>
+        <v>0.994807472454422</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.986363710014053</v>
+        <v>0.990683501795511</v>
       </c>
     </row>
     <row r="53">
@@ -4439,46 +4497,46 @@
         <v>87.96</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.00703046809654</v>
+        <v>1.00524329944529</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>87.1563317288414</v>
+        <v>87.3316460387752</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>88.3741783436544</v>
+        <v>88.112215630015</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>86.7126207468126</v>
+        <v>86.8724691813583</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>87.3459173149542</v>
+        <v>87.5012049804637</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>87.3459173149542</v>
+        <v>87.5012049804637</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>87.3459173149542</v>
+        <v>87.5012049804637</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>87.3459173149542</v>
+        <v>87.5012049804637</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0036412976751737</v>
+        <v>0.0046861029564282</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.0192586163810404</v>
+        <v>-0.0202213368276847</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.00364793525357432</v>
+        <v>0.00469709990779266</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00217523595076</v>
+        <v>1.0019415521106</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.988364689234205</v>
+        <v>0.993065539832559</v>
       </c>
     </row>
     <row r="54">
@@ -4498,46 +4556,46 @@
         <v>94.997</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.02902413055998</v>
+        <v>1.02975825400272</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>85.7807092490646</v>
+        <v>85.9869126932651</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>88.5681147299447</v>
+        <v>88.3564725806384</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>87.1040711664562</v>
+        <v>87.2611312622853</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>92.3175629985509</v>
+        <v>92.2517490204542</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>85.7807092490646</v>
+        <v>85.9869126932651</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>85.7807092490646</v>
+        <v>85.9869126932651</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>85.7807092490646</v>
+        <v>85.9869126932651</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0180821488174305</v>
+        <v>-0.0174574577860726</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.0181628815602347</v>
+        <v>-0.0156087278992079</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.017919647695103</v>
+        <v>-0.0173059592440666</v>
       </c>
       <c r="R54" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.968528115458038</v>
+        <v>0.973181818850783</v>
       </c>
     </row>
     <row r="55">
@@ -4557,46 +4615,46 @@
         <v>76.449</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.974840666684381</v>
+        <v>0.975514719226065</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>82.92982069478</v>
+        <v>83.0807294080992</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>88.8124402882801</v>
+        <v>88.6435335227149</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>87.6044015467648</v>
+        <v>87.7458059903597</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>78.4220464047911</v>
+        <v>78.3678590320519</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>82.92982069478</v>
+        <v>83.0807294080992</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>82.92982069478</v>
+        <v>83.0807294080992</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>82.92982069478</v>
+        <v>83.0807294080992</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.0337994309545554</v>
+        <v>-0.0343823281314672</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0617799361923288</v>
+        <v>-0.0571541366648393</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0332346115955632</v>
+        <v>-0.0337979722045948</v>
       </c>
       <c r="R55" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.933763563140418</v>
+        <v>0.937245235004196</v>
       </c>
     </row>
     <row r="56">
@@ -4616,46 +4674,46 @@
         <v>81.448</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.99065585771467</v>
+        <v>0.990287732021796</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>83.0931884371278</v>
+        <v>83.1612726445922</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>89.1044492180252</v>
+        <v>88.9715315236315</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>88.2184451067854</v>
+        <v>88.3338663516325</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>82.2162402470331</v>
+        <v>82.2468029909991</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>82.2162402470331</v>
+        <v>82.2468029909991</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>82.2162402470331</v>
+        <v>82.2468029909991</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>82.2162402470331</v>
+        <v>82.2468029909991</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.00864186387042496</v>
+        <v>-0.0100882590768053</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.055294599852816</v>
+        <v>-0.0556344400034974</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.00860463029786562</v>
+        <v>-0.0100375432791853</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>0.989446208448744</v>
+        <v>0.98900365970226</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.922695117567725</v>
+        <v>0.924417075692957</v>
       </c>
     </row>
     <row r="57">
@@ -4675,46 +4733,46 @@
         <v>88.796</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.00470906196413</v>
+        <v>1.00427650538007</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>88.3687629574529</v>
+        <v>88.3600834698856</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>89.4377590812989</v>
+        <v>89.3351228982038</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>88.9276621613051</v>
+        <v>89.0093599492433</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>88.3798139795918</v>
+        <v>88.4178804585247</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>88.3798139795918</v>
+        <v>88.4178804585247</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>88.3798139795918</v>
+        <v>88.4178804585247</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>88.3798139795918</v>
+        <v>88.4178804585247</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0722907424579108</v>
+        <v>0.0723496973409278</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.0118368058453104</v>
+        <v>0.0104761469086705</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0749678374252964</v>
+        <v>0.0750312138965568</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00012505575238</v>
+        <v>1.00065410744727</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.988171158215789</v>
+        <v>0.989732566431635</v>
       </c>
     </row>
     <row r="58">
@@ -4734,46 +4792,46 @@
         <v>96.617</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.03102637919806</v>
+        <v>1.03190947377405</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>91.8901065064685</v>
+        <v>91.8592097707297</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>89.8016823096131</v>
+        <v>89.7247610059143</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>89.6835020008119</v>
+        <v>89.7258990695284</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>93.7095325098757</v>
+        <v>93.6293371226046</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>93.7095325098757</v>
+        <v>93.6293371226046</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>93.7095325098757</v>
+        <v>93.6293371226046</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>93.7095325098757</v>
+        <v>93.6293371226046</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0585563235125302</v>
+        <v>0.0572695483508036</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.0924313092095066</v>
+        <v>0.0888789257570131</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0603047040980935</v>
+        <v>0.0589412077857308</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>1.01980002061788</v>
+        <v>1.01927000413233</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.04351644757377</v>
+        <v>1.04351726405193</v>
       </c>
     </row>
     <row r="59">
@@ -4793,46 +4851,46 @@
         <v>88.033</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.97086178521567</v>
+        <v>0.970418169708357</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>93.4087113231365</v>
+        <v>93.4408802316494</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>90.1848701187912</v>
+        <v>90.130325929721</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>90.4346746748855</v>
+        <v>90.4341386013708</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>90.6751108557065</v>
+        <v>90.7165619399489</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>90.6751108557065</v>
+        <v>90.7165619399489</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>90.6751108557065</v>
+        <v>90.7165619399489</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>90.6751108557065</v>
+        <v>90.7165619399489</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>-0.0329170107043704</v>
+        <v>-0.0316038233974546</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.0933957181631049</v>
+        <v>0.0919085880233654</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>-0.032381141735494</v>
+        <v>-0.0311096422571218</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.970735058553871</v>
+        <v>0.970844471017967</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.00543595323993</v>
+        <v>1.00650431477065</v>
       </c>
     </row>
     <row r="60">
@@ -4852,46 +4910,46 @@
         <v>96.158</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.996196705689752</v>
+        <v>0.99519373768435</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>93.7106050681502</v>
+        <v>93.7668967815551</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>90.5784161310318</v>
+        <v>90.5441381126544</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>91.1500203856508</v>
+        <v>91.1042506239187</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>96.525113414646</v>
+        <v>96.6223925642294</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>96.525113414646</v>
+        <v>96.6223925642294</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>96.525113414646</v>
+        <v>96.6223925642294</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>96.525113414646</v>
+        <v>96.6223925642294</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0625203093974323</v>
+        <v>0.0630705796645037</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.174039497848835</v>
+        <v>0.174785998366447</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0645160783784284</v>
+        <v>0.0651020111210781</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>1.03003404304613</v>
+        <v>1.03045313304253</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.06565247591669</v>
+        <v>1.06713029223396</v>
       </c>
     </row>
     <row r="61">
@@ -4911,46 +4969,46 @@
         <v>91.528</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.0027271350824</v>
+        <v>1.00373906064027</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>93.1564219231282</v>
+        <v>93.0730461442715</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>90.9737203689939</v>
+        <v>90.9588843952519</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>91.7995815161371</v>
+        <v>91.7078193330132</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>91.2790696468772</v>
+        <v>91.1870461050063</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>91.2790696468772</v>
+        <v>91.1870461050063</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>91.2790696468772</v>
+        <v>91.1870461050063</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>91.2790696468772</v>
+        <v>91.1870461050063</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0558817039244067</v>
+        <v>-0.0578976727688933</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0328045006742694</v>
+        <v>0.0313190684069893</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.054349003924328</v>
+        <v>-0.0562534865363635</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.979847312321632</v>
+        <v>0.979736345618884</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.00335645587148</v>
+        <v>1.00250840488284</v>
       </c>
     </row>
     <row r="62">
@@ -4970,46 +5028,46 @@
         <v>95.906</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.02806988819732</v>
+        <v>1.02969863719356</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>93.2974777219079</v>
+        <v>93.2198120997934</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>91.3658995411389</v>
+        <v>91.3710505270826</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>92.3802759145182</v>
+        <v>92.2440196341969</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>93.2874322077144</v>
+        <v>93.1398727120699</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>93.2874322077144</v>
+        <v>93.1398727120699</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>93.2874322077144</v>
+        <v>93.1398727120699</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>93.2874322077144</v>
+        <v>93.1398727120699</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.0217638825523512</v>
+        <v>0.021189522253581</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.00450434753920903</v>
+        <v>-0.00522768210880042</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.0220024433707178</v>
+        <v>0.0214156142837967</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.999892328126775</v>
+        <v>0.999142463539425</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>1.02103117986279</v>
+        <v>1.01935867186361</v>
       </c>
     </row>
     <row r="63">
@@ -5029,46 +5087,46 @@
         <v>92.486</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.970137239149842</v>
+        <v>0.968189397627199</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>93.6439336192717</v>
+        <v>93.8112596129938</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>91.7502611992269</v>
+        <v>91.7772648587846</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>92.8864188696219</v>
+        <v>92.7094225668725</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>95.332903704478</v>
+        <v>95.5246981909336</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>95.332903704478</v>
+        <v>95.5246981909336</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>95.332903704478</v>
+        <v>95.5246981909336</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>95.332903704478</v>
+        <v>95.5246981909336</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.0216896197907418</v>
+        <v>0.0252824629275315</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.0513679311204098</v>
+        <v>0.053001746849352</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.0219265494649818</v>
+        <v>0.0256047749414059</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.0180360864813</v>
+        <v>1.01826474332621</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.03904776355319</v>
+        <v>1.04083182624711</v>
       </c>
     </row>
     <row r="64">
@@ -5088,46 +5146,46 @@
         <v>90.384</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.00358226361332</v>
+        <v>1.00096736679502</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>91.9651545573478</v>
+        <v>92.0653320880057</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>92.1233138529344</v>
+        <v>92.1752612548616</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>93.3168614517419</v>
+        <v>93.1050784358321</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>90.0613764083269</v>
+        <v>90.29665001907</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>90.0613764083269</v>
+        <v>90.29665001907</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>90.0613764083269</v>
+        <v>90.29665001907</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>90.0613764083269</v>
+        <v>90.29665001907</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.056883617551535</v>
+        <v>-0.0562844724650912</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0669643036683371</v>
+        <v>-0.0654687011704288</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.0552959900654261</v>
+        <v>-0.0547298057033779</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.979298918615597</v>
+        <v>0.980788837352533</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.977617637073942</v>
+        <v>0.979619138473638</v>
       </c>
     </row>
     <row r="65">
@@ -5147,46 +5205,46 @@
         <v>93.156</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00037685835852</v>
+        <v>1.00441788976592</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>92.0628509182644</v>
+        <v>91.83688015498</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>92.4838051635041</v>
+        <v>92.5651157256495</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>93.6826871553463</v>
+        <v>93.4461139239878</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>93.1209066079918</v>
+        <v>92.7462572592271</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>93.1209066079918</v>
+        <v>92.7462572592271</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>93.1209066079918</v>
+        <v>92.7462572592271</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>93.1209066079918</v>
+        <v>92.7462572592271</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0334073218526309</v>
+        <v>0.0267669862874838</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.0201780864796279</v>
+        <v>0.0170990422523973</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.0339716127121283</v>
+        <v>0.0271284398661495</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.0114927539086</v>
+        <v>1.00990209056223</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.00688878926815</v>
+        <v>1.00195690927578</v>
       </c>
     </row>
     <row r="66">
@@ -5206,46 +5264,46 @@
         <v>96.275</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.02168155964132</v>
+        <v>1.02337163268179</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>94.9022715361447</v>
+        <v>94.757079904479</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>92.8291940812753</v>
+        <v>92.9457301494622</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>93.9787020496859</v>
+        <v>93.7336135721683</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>94.2319053245897</v>
+        <v>94.0762836543624</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>94.2319053245897</v>
+        <v>94.0762836543624</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>94.2319053245897</v>
+        <v>94.0762836543624</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>94.2319053245897</v>
+        <v>94.0762836543624</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0118601021041621</v>
+        <v>0.0142386337238108</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.0101243339485679</v>
+        <v>0.0100538138503503</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0119307119858143</v>
+        <v>0.0143404859068095</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.992936246933777</v>
+        <v>0.992815352153075</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>1.01511066919407</v>
+        <v>1.01216358732222</v>
       </c>
     </row>
     <row r="67">
@@ -5265,46 +5323,46 @@
         <v>94.864</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.972719731411302</v>
+        <v>0.969242776599726</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>97.254372798807</v>
+        <v>97.6215503495521</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>93.1573377449905</v>
+        <v>93.3161196180722</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>94.1969033012749</v>
+        <v>93.9651626378781</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>97.5244944012429</v>
+        <v>97.8743430338471</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>97.5244944012429</v>
+        <v>97.8743430338471</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>97.5244944012429</v>
+        <v>97.8743430338471</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>97.5244944012429</v>
+        <v>97.8743430338471</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0343447491298497</v>
+        <v>0.039578460593677</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.0229888172037498</v>
+        <v>0.024597249584783</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0349413403593146</v>
+        <v>0.0403721238972286</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00277747513723</v>
+        <v>1.00258951720588</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.04687936304285</v>
+        <v>1.04884711703006</v>
       </c>
     </row>
     <row r="68">
@@ -5324,46 +5382,46 @@
         <v>98.771</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1.0078771549852</v>
+        <v>1.00319682410812</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>97.4057738484578</v>
+        <v>97.5627297462889</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>93.466969987919</v>
+        <v>93.676005819192</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>94.330554093002</v>
+        <v>94.140059729033</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>97.9990463237064</v>
+        <v>98.4562526778443</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>97.9990463237064</v>
+        <v>98.4562526778443</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>97.9990463237064</v>
+        <v>98.4562526778443</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>97.9990463237064</v>
+        <v>98.4562526778443</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.00485417615215927</v>
+        <v>0.00592787227987797</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.088136227003583</v>
+        <v>0.0903644006400135</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.00486597675155376</v>
+        <v>0.00594547688351788</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00609073211791</v>
+        <v>1.00915844538052</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.04848853382508</v>
+        <v>1.05102957600347</v>
       </c>
     </row>
     <row r="69">
@@ -5383,46 +5441,46 @@
         <v>94.481</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.00155051540205</v>
+        <v>1.0096213775425</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>95.223047213068</v>
+        <v>94.8969340104778</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>93.7595541162406</v>
+        <v>94.0279593301696</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>94.3895555632557</v>
+        <v>94.2771493555285</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>94.3347325442419</v>
+        <v>93.5806254716737</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>94.3347325442419</v>
+        <v>93.5806254716737</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>94.3347325442419</v>
+        <v>93.5806254716737</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>94.3347325442419</v>
+        <v>93.5806254716737</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>-0.0381083057428727</v>
+        <v>-0.0507889450368825</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.0130349454323919</v>
+        <v>0.00899624671769295</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>-0.0373913208028648</v>
+        <v>-0.049520747271623</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.990671221990634</v>
+        <v>0.986129072002909</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.00613461138358</v>
+        <v>0.995242544221075</v>
       </c>
     </row>
     <row r="70">
@@ -5442,46 +5500,46 @@
         <v>94.508</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.01305029980528</v>
+        <v>1.01430635111233</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>92.0072924992567</v>
+        <v>91.6572033694508</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>94.0393859838446</v>
+        <v>94.3775383826392</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>94.402151311578</v>
+        <v>94.4168569920041</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>93.2905306065904</v>
+        <v>93.1750056542174</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>93.2905306065904</v>
+        <v>93.1750056542174</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>93.2905306065904</v>
+        <v>93.1750056542174</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>93.2905306065904</v>
+        <v>93.1750056542174</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>-0.0111308328215691</v>
+        <v>-0.00434386318440928</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>-0.00998997860392081</v>
+        <v>-0.00958028915615161</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>-0.0110691143069898</v>
+        <v>-0.00433444225673696</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.01394713475939</v>
+        <v>1.01655955264802</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.992036790017079</v>
+        <v>0.987258274065739</v>
       </c>
     </row>
     <row r="71">
@@ -5501,46 +5559,46 @@
         <v>86.553</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.976643482795271</v>
+        <v>0.971482184569185</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0.675014910867725</v>
+        <v>0.941355768761722</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>91.5892690648246</v>
+        <v>91.3168122953784</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>94.311120931138</v>
+        <v>94.7300216245737</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>94.3963108224158</v>
+        <v>94.5961254936801</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>88.6229228216165</v>
+        <v>89.0937593862135</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>89.5869411198626</v>
+        <v>89.2241286150735</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>89.5869411198626</v>
+        <v>89.2241286150735</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>89.5869411198626</v>
+        <v>89.2241286150735</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>-0.0405090457392915</v>
+        <v>-0.0433280028727929</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>-0.081390355624126</v>
+        <v>-0.0883808171849714</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>-0.0396995221556397</v>
+        <v>-0.0424027560975536</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.978137963481893</v>
+        <v>0.977083259613401</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>0.949908560468444</v>
+        <v>0.941878056026201</v>
       </c>
     </row>
     <row r="72">
@@ -5560,46 +5618,46 @@
         <v>96.169</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1.0103605401184</v>
+        <v>1.00387409125835</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>1</v>
+        <v>0.568355099410975</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>93.5870845120958</v>
+        <v>92.7706237364321</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>94.578946263917</v>
+        <v>95.0899361209906</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>94.3944454766913</v>
+        <v>94.845688459088</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>95.1828542202671</v>
+        <v>95.797870308071</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>95.1828542202671</v>
+        <v>94.4911747625974</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>95.1828542202671</v>
+        <v>94.4911747625974</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>95.1828542202671</v>
+        <v>94.4911747625974</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0605902599198517</v>
+        <v>0.0573549382067389</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>-0.0287369337670588</v>
+        <v>-0.0402724845543421</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0624634911121413</v>
+        <v>0.0590316344836139</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.01705117449155</v>
+        <v>1.01854629145379</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.00638522610164</v>
+        <v>0.993703210004986</v>
       </c>
     </row>
     <row r="73">
@@ -5619,46 +5677,46 @@
         <v>94.588</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.00290675162852</v>
+        <v>1.015047749916</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>94.3462228020955</v>
+        <v>93.4654269169376</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>94.8440966755957</v>
+        <v>95.4583677537765</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>94.3949198068137</v>
+        <v>95.1694195023659</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>94.3138530540432</v>
+        <v>93.18576392867</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>94.3138530540432</v>
+        <v>93.18576392867</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>94.3138530540432</v>
+        <v>93.18576392867</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>94.3138530540432</v>
+        <v>93.18576392867</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>-0.00917173992595572</v>
+        <v>-0.0139114789051219</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>-0.000221334068964629</v>
+        <v>-0.00421947963067737</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>-0.0091298078140517</v>
+        <v>-0.0138151614392269</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.999656904674178</v>
+        <v>0.997007845601388</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.994409313387568</v>
+        <v>0.976192722769276</v>
       </c>
     </row>
     <row r="74">
@@ -5678,46 +5736,46 @@
         <v>93.383</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.00725601148571</v>
+        <v>1.00757573004315</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>94.002690600209</v>
+        <v>93.5632673272589</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>95.1081843020609</v>
+        <v>95.8360281789691</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>94.40004038891</v>
+        <v>95.5694196691698</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>92.7102930487944</v>
+        <v>92.6808747130112</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>92.7102930487944</v>
+        <v>92.6808747130112</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>92.7102930487944</v>
+        <v>92.6808747130112</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>92.7102930487944</v>
+        <v>92.6808747130112</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.0171485803898036</v>
+        <v>-0.00543282496729585</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>-0.0062196833271625</v>
+        <v>-0.00530325635868478</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.0170023803855188</v>
+        <v>-0.00541809386297698</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.986251483407947</v>
+        <v>0.990569027360264</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>0.974787750698186</v>
+        <v>0.967077585268186</v>
       </c>
     </row>
     <row r="75">
@@ -5737,113 +5795,165 @@
         <v>93.705</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.978936670472697</v>
+        <v>0.97254647663407</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>93.9414902312745</v>
+        <v>94.8377946112152</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>95.372489876936</v>
+        <v>96.2222086752152</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>94.4117084653437</v>
+        <v>96.0378717272871</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>95.7212073328021</v>
+        <v>96.3501511252273</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>95.7212073328021</v>
+        <v>96.3501511252273</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>95.7212073328021</v>
+        <v>96.3501511252273</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>95.7212073328021</v>
+        <v>96.3501511252273</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>0.0319603735995705</v>
+        <v>0.0388268258510686</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.068472772217238</v>
+        <v>0.0798665408198784</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>0.0324765911636482</v>
+        <v>0.0395904378716549</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1.01894495283337</v>
+        <v>1.01594677016913</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.00365637361797</v>
+        <v>1.00132965613421</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
         <v>126</v>
       </c>
-      <c r="B76" s="2"/>
+      <c r="B76" s="2" t="n">
+        <v>95.89</v>
+      </c>
       <c r="C76" s="3" t="n">
-        <v>92.1158057568289</v>
+        <v>95.89</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>103.512753656446</v>
+        <v>95.89</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>81.9736831501191</v>
+        <v>95.89</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>1.01121254939042</v>
-      </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="13"/>
+        <v>1.0031011206711</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>97.6554356024809</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>96.6142285502455</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>96.5525157197244</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>95.5935528572106</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>95.5935528572106</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>95.5935528572106</v>
+      </c>
       <c r="N76" s="14" t="n">
-        <v>91.0944052388968</v>
-      </c>
-      <c r="O76" s="15"/>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="17"/>
-      <c r="R76" s="18"/>
-      <c r="S76" s="19"/>
+        <v>95.5935528572106</v>
+      </c>
+      <c r="O76" s="15" t="n">
+        <v>-0.0078835843106085</v>
+      </c>
+      <c r="P76" s="16" t="n">
+        <v>0.0116664661793318</v>
+      </c>
+      <c r="Q76" s="17" t="n">
+        <v>-0.0078525903611022</v>
+      </c>
+      <c r="R76" s="18" t="n">
+        <v>0.978886144610901</v>
+      </c>
+      <c r="S76" s="19" t="n">
+        <v>0.989435555110766</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
         <v>127</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="n">
+        <v>106.453</v>
+      </c>
       <c r="C77" s="3" t="n">
-        <v>91.1816207130325</v>
+        <v>106.453</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>104.582326429684</v>
+        <v>106.453</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>79.4980207429723</v>
+        <v>106.453</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.00402873583958</v>
-      </c>
-      <c r="G77" s="7"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="12"/>
-      <c r="M77" s="13"/>
+        <v>1.01967576917357</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>0.44890997366091</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>100.393094545403</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>97.009487075822</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>97.0926530864779</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>104.39887189462</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <v>102.191327949732</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>102.191327949732</v>
+      </c>
       <c r="N77" s="14" t="n">
-        <v>90.8157480540489</v>
-      </c>
-      <c r="O77" s="15"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="17"/>
-      <c r="R77" s="18"/>
-      <c r="S77" s="19"/>
+        <v>102.191327949732</v>
+      </c>
+      <c r="O77" s="15" t="n">
+        <v>0.0667414413973424</v>
+      </c>
+      <c r="P77" s="16" t="n">
+        <v>0.0966409850753069</v>
+      </c>
+      <c r="Q77" s="17" t="n">
+        <v>0.0690190383694202</v>
+      </c>
+      <c r="R77" s="18" t="n">
+        <v>1.01791192325001</v>
+      </c>
+      <c r="S77" s="19" t="n">
+        <v>1.05341581560842</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
@@ -5851,16 +5961,16 @@
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="3" t="n">
-        <v>90.4799819507849</v>
+        <v>101.208403846438</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>104.925036438899</v>
+        <v>113.480917930405</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>78.0235815174738</v>
+        <v>90.2631137987933</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.00539834390196</v>
+        <v>1.00495774959793</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
@@ -5870,7 +5980,7 @@
       <c r="L78" s="12"/>
       <c r="M78" s="13"/>
       <c r="N78" s="14" t="n">
-        <v>89.9941625123742</v>
+        <v>100.709113280563</v>
       </c>
       <c r="O78" s="15"/>
       <c r="P78" s="16"/>
@@ -5884,16 +5994,16 @@
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
-        <v>89.9518568417642</v>
+        <v>98.8813631784681</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>104.975643001751</v>
+        <v>112.447197012806</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>77.0782280337762</v>
+        <v>86.9521361472322</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.978567281984112</v>
+        <v>0.970826101468984</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -5903,7 +6013,7 @@
       <c r="L79" s="12"/>
       <c r="M79" s="13"/>
       <c r="N79" s="14" t="n">
-        <v>91.9219950409344</v>
+        <v>101.852806624016</v>
       </c>
       <c r="O79" s="15"/>
       <c r="P79" s="16"/>
@@ -5916,10 +6026,18 @@
         <v>130</v>
       </c>
       <c r="B80" s="2"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
+      <c r="C80" s="3" t="n">
+        <v>99.2357255735799</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>113.224820032587</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>86.9750044847108</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>1.00420997478367</v>
+      </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
       <c r="I80" s="9"/>
@@ -5927,7 +6045,9 @@
       <c r="K80" s="11"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13"/>
-      <c r="N80" s="14"/>
+      <c r="N80" s="14" t="n">
+        <v>98.8196971404885</v>
+      </c>
       <c r="O80" s="15"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="17"/>
@@ -5939,10 +6059,18 @@
         <v>131</v>
       </c>
       <c r="B81" s="2"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
+      <c r="C81" s="3" t="n">
+        <v>99.5913579017007</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>114.009261884485</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>86.9967790753179</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>1.02154033754046</v>
+      </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
       <c r="I81" s="9"/>
@@ -5950,7 +6078,9 @@
       <c r="K81" s="11"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13"/>
-      <c r="N81" s="14"/>
+      <c r="N81" s="14" t="n">
+        <v>97.491361076827</v>
+      </c>
       <c r="O81" s="15"/>
       <c r="P81" s="16"/>
       <c r="Q81" s="17"/>
@@ -6338,150 +6468,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="1"/>
+        <v>149</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" s="1"/>
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>151</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>-0.0748681845281545</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>-0.013654181826719</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>-0.0514837025120527</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>0.0042740975344412</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0.0231146307465903</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>0.134051840054528</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>0.0695479171345147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>-0.0129638443979727</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>0.0248850261261399</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="1"/>
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="1"/>
+      <c r="A15" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="1"/>
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="1"/>
+      <c r="A17" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="1"/>
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="1"/>
+      <c r="A19" t="s">
+        <v>166</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6489,235 +6567,160 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90796628-22A3-4B4F-B33E-D0626A7214E6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21DFBDC1-6133-4205-B1AD-F6C10DF74222}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE5C20C2-FFAE-4D1C-A5D4-F92FF1CBE400}"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>-0.0635556317042623</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.0571923295857162</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>-0.00576964615224479</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.00444130168196096</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>-0.00858957182551023</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.0684349357195195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.0170485801385565</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.0155757246686487</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.0638351229341675</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/indicadores/GSF-EPRIV-FOR_out.xlsx
+++ b/indicadores/GSF-EPRIV-FOR_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocupados en el sector privado formal en el Gran Santa Fe</t>
+    <t xml:space="preserve">Ocupados en el sector privado formal</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -74,6 +74,12 @@
     <t xml:space="preserve">const</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglomerado Gran Santa Fe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -107,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/05/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">vcorvalan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1050,9 +1056,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1063,7 +1073,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1077,12 +1087,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.0684349357195195</v>
+        <v>0.0662343912007149</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1093,7 +1103,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1121,7 +1131,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1135,12 +1145,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.0000737807441455992</v>
+        <v>0.000119238592367948</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1163,7 +1173,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1177,7 +1187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1191,7 +1201,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1205,12 +1215,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.777269304951627</v>
+        <v>0.836746843176354</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1221,7 +1231,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1235,12 +1245,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.841567002084579</v>
+        <v>0.846814191525197</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1383,10 +1393,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1399,10 +1409,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1426,66 +1436,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>74.903</v>
@@ -1538,7 +1548,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>64.085</v>
@@ -1595,7 +1605,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>69.046</v>
@@ -1652,7 +1662,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>76.437</v>
@@ -1709,7 +1719,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>71.583</v>
@@ -1768,7 +1778,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>72.422</v>
@@ -1827,7 +1837,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>73.236</v>
@@ -1886,7 +1896,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>82.639</v>
@@ -1945,7 +1955,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>82.172</v>
@@ -2004,7 +2014,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>76.665</v>
@@ -2063,7 +2073,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>71.122</v>
@@ -2122,7 +2132,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>79.78</v>
@@ -2181,7 +2191,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>81.632</v>
@@ -2240,7 +2250,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>71.358</v>
@@ -2299,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>75.162</v>
@@ -2358,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>75.163</v>
@@ -2417,7 +2427,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>81.025</v>
@@ -2476,7 +2486,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>81.906</v>
@@ -2535,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>79.225</v>
@@ -2594,7 +2604,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>72.614</v>
@@ -2653,7 +2663,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>81.115</v>
@@ -2712,7 +2722,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>93.59</v>
@@ -2771,7 +2781,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>88.207</v>
@@ -2830,7 +2840,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>89.865</v>
@@ -2889,7 +2899,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>88.789</v>
@@ -2948,7 +2958,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>91.875</v>
@@ -3007,7 +3017,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>87.797</v>
@@ -3066,7 +3076,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>83.817</v>
@@ -3125,7 +3135,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>81.62</v>
@@ -3184,7 +3194,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>85.937</v>
@@ -3243,7 +3253,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>94.097</v>
@@ -3302,7 +3312,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>88.379</v>
@@ -3361,7 +3371,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>95.958</v>
@@ -3420,7 +3430,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>99.608</v>
@@ -3479,7 +3489,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>90.0095</v>
@@ -3538,7 +3548,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>86.652</v>
@@ -3597,7 +3607,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>91.424</v>
@@ -3656,7 +3666,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>95.267</v>
@@ -3715,7 +3725,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>85.922</v>
@@ -3774,7 +3784,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>84.925</v>
@@ -3833,7 +3843,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>86.89</v>
@@ -3892,7 +3902,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>89.474</v>
@@ -3951,7 +3961,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>87.112</v>
@@ -4010,7 +4020,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>85.925</v>
@@ -4069,7 +4079,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>83.698</v>
@@ -4128,7 +4138,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>80.547</v>
@@ -4187,7 +4197,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>84.243</v>
@@ -4246,7 +4256,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>92.858</v>
@@ -4305,7 +4315,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>89.564</v>
@@ -4364,7 +4374,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>86.82</v>
@@ -4423,7 +4433,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>85.782</v>
@@ -4482,7 +4492,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>87.96</v>
@@ -4541,7 +4551,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>94.997</v>
@@ -4600,7 +4610,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>76.449</v>
@@ -4659,7 +4669,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>81.448</v>
@@ -4718,7 +4728,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>88.796</v>
@@ -4777,7 +4787,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>96.617</v>
@@ -4836,7 +4846,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>88.033</v>
@@ -4895,7 +4905,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>96.158</v>
@@ -4954,7 +4964,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>91.528</v>
@@ -5013,7 +5023,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>95.906</v>
@@ -5072,7 +5082,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>92.486</v>
@@ -5131,7 +5141,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>90.384</v>
@@ -5190,7 +5200,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>93.156</v>
@@ -5249,7 +5259,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>96.275</v>
@@ -5308,7 +5318,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>94.864</v>
@@ -5367,7 +5377,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>98.771</v>
@@ -5426,7 +5436,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>94.481</v>
@@ -5485,7 +5495,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>94.508</v>
@@ -5544,7 +5554,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>86.553</v>
@@ -5603,7 +5613,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>96.169</v>
@@ -5662,7 +5672,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>94.588</v>
@@ -5721,7 +5731,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>93.383</v>
@@ -5780,7 +5790,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>93.705</v>
@@ -5839,7 +5849,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>95.89</v>
@@ -5898,7 +5908,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>106.453</v>
@@ -5957,7 +5967,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="3" t="n">
@@ -5990,7 +6000,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
@@ -6023,7 +6033,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3" t="n">
@@ -6056,7 +6066,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="3" t="n">
@@ -6089,7 +6099,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
@@ -6112,7 +6122,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -6135,7 +6145,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="3"/>
@@ -6158,7 +6168,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="3"/>
@@ -6181,7 +6191,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="3"/>
@@ -6204,7 +6214,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="3"/>
@@ -6227,7 +6237,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="3"/>
@@ -6250,7 +6260,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3"/>
@@ -6273,7 +6283,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3"/>
@@ -6296,7 +6306,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3"/>
@@ -6319,7 +6329,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
@@ -6342,7 +6352,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3"/>
@@ -6365,7 +6375,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
@@ -6388,7 +6398,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
@@ -6411,7 +6421,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -6434,7 +6444,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
@@ -6468,97 +6478,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -6582,7 +6592,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -6592,80 +6602,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0635556317042623</v>
+        <v>-0.0513481891249785</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0571923295857162</v>
+        <v>0.0510780830098253</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.00576964615224479</v>
+        <v>-0.00544327674559669</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.00444130168196096</v>
+        <v>0.000659657951635425</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>-0.00858957182551023</v>
+        <v>-0.010919642501838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.0684349357195195</v>
+        <v>0.0662343912007149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.0170485801385565</v>
+        <v>0.0261872563151287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.0155757246686487</v>
+        <v>0.0104029622417957</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0638351229341675</v>
+        <v>0.0623526222207706</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/GSF-EPRIV-FOR_out.xlsx
+++ b/indicadores/GSF-EPRIV-FOR_out.xlsx
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">04/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1072,9 +1072,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1086,14 +1084,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>0.0662343912007149</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1103,13 +1097,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1118,10 +1110,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.0746937342624868</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1131,11 +1127,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1144,14 +1142,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.000119238592367948</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1160,7 +1154,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1173,11 +1169,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.000563429283617215</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1186,9 +1184,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1201,7 +1197,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1215,13 +1211,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.836746843176354</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1231,7 +1225,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1250,7 +1244,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.846814191525197</v>
+        <v>0.833601941511351</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1260,7 +1254,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1272,10 +1268,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.780838353316533</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1510,40 +1510,40 @@
         <v>74.903</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.02695157301084</v>
+        <v>1.02695157313424</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>72.1116082717147</v>
+        <v>72.1116082586609</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>71.4790567400052</v>
+        <v>71.4789309075171</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>71.7119052311341</v>
+        <v>71.7119060269498</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>72.9372270012671</v>
+        <v>72.9372269925029</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>72.9372270012671</v>
+        <v>72.9372269925029</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>72.9372270012671</v>
+        <v>72.9372269925029</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>72.9372270012671</v>
+        <v>72.9372269925029</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>1.01144917925615</v>
+        <v>1.01144917931771</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.0203999650774</v>
+        <v>1.02040176128085</v>
       </c>
     </row>
     <row r="3">
@@ -1563,44 +1563,44 @@
         <v>64.085</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.98061921515686</v>
+        <v>0.98061921548474</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>71.2840631052938</v>
+        <v>71.2840630846766</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>72.0565050056373</v>
+        <v>72.0564042216837</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>72.2640352054344</v>
+        <v>72.2640358356032</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>65.3515646129257</v>
+        <v>65.3515645910747</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>71.2840631052938</v>
+        <v>71.2840630846766</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>71.2840631052938</v>
+        <v>71.2840630846766</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>71.2840631052938</v>
+        <v>71.2840630846766</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>-0.0229263835501995</v>
+        <v>-0.0229263837192638</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>-0.0226655709840001</v>
+        <v>-0.0226655711492325</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.989280053198762</v>
+        <v>0.989281436600264</v>
       </c>
     </row>
     <row r="4">
@@ -1620,44 +1620,44 @@
         <v>69.046</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.957106122496083</v>
+        <v>0.957106122697761</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>72.2321515893076</v>
+        <v>72.2321515898545</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>72.6348646276828</v>
+        <v>72.6347889709035</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>72.8222917885853</v>
+        <v>72.8222922490844</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>72.1403806507178</v>
+        <v>72.1403806355167</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>72.1403806507178</v>
+        <v>72.1403806355167</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>72.1403806507178</v>
+        <v>72.1403806355167</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>72.1403806507178</v>
+        <v>72.1403806355167</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.0119411684406761</v>
+        <v>0.0119411685191854</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0120127488266091</v>
+        <v>0.0120127489060615</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.998729500138504</v>
+        <v>0.998729499920494</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.993192195242607</v>
+        <v>0.993193229547554</v>
       </c>
     </row>
     <row r="5">
@@ -1677,44 +1677,44 @@
         <v>76.437</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.0343346955722</v>
+        <v>1.03433469486655</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>72.4342922425735</v>
+        <v>72.4342922687588</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>73.2145641863671</v>
+        <v>73.2145138770188</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>73.3879017289369</v>
+        <v>73.3879020084665</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>73.8996770844225</v>
+        <v>73.8996771348388</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>73.8996770844225</v>
+        <v>73.8996771348388</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>73.8996770844225</v>
+        <v>73.8996771348388</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>73.8996770844225</v>
+        <v>73.8996771348388</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0240945062986562</v>
+        <v>0.0240945071915987</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.0243871243516529</v>
+        <v>0.0243871252663717</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>1.02023053993462</v>
+        <v>1.02023054026183</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.00935760399135</v>
+        <v>1.00935829825997</v>
       </c>
     </row>
     <row r="6">
@@ -1734,46 +1734,46 @@
         <v>71.583</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.02658470552998</v>
+        <v>1.02658470564039</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>71.4921596347977</v>
+        <v>71.4921596342925</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>73.7957232094302</v>
+        <v>73.7956986566626</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>73.9586822191497</v>
+        <v>73.9586822967547</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>69.7292679448647</v>
+        <v>69.7292679373653</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>69.7292679448647</v>
+        <v>69.7292679373653</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>69.7292679448647</v>
+        <v>69.7292679373653</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>69.7292679448647</v>
+        <v>69.7292679373653</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>-0.0580883155623013</v>
+        <v>-0.0580883163520782</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.0439824653101593</v>
+        <v>-0.0439824652981035</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>-0.056433387858969</v>
+        <v>-0.0564333886041761</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>0.975341468226189</v>
+        <v>0.975341468128183</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.944895786805625</v>
+        <v>0.944896101082848</v>
       </c>
     </row>
     <row r="7">
@@ -1793,46 +1793,46 @@
         <v>72.422</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.982023819624594</v>
+        <v>0.982023820152276</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>72.7337425304775</v>
+        <v>72.7337425014254</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>74.3788894201735</v>
+        <v>74.3788912535039</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>74.5350093286618</v>
+        <v>74.5350091725864</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>73.7477019933033</v>
+        <v>73.7477019536756</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>73.7477019933033</v>
+        <v>73.7477019536756</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>73.7477019933033</v>
+        <v>73.7477019536756</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>73.7477019933033</v>
+        <v>73.7477019536756</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0560296925682447</v>
+        <v>0.0560296921384543</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.0345608650894447</v>
+        <v>0.034560864832754</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0576290869942304</v>
+        <v>0.0576290865396716</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>1.01394070245184</v>
+        <v>1.013940702312</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.991513890140192</v>
+        <v>0.991513865168049</v>
       </c>
     </row>
     <row r="8">
@@ -1852,46 +1852,46 @@
         <v>73.236</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.962812907764574</v>
+        <v>0.962812907662043</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>76.8734434144886</v>
+        <v>76.8734434273124</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>74.9620690073577</v>
+        <v>74.9620980920121</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>75.0961120555399</v>
+        <v>75.0961116228015</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>76.0646221185763</v>
+        <v>76.0646221266765</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>76.0646221185763</v>
+        <v>76.0646221266765</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>76.0646221185763</v>
+        <v>76.0646221266765</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>76.0646221185763</v>
+        <v>76.0646221266765</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.030933434705969</v>
+        <v>0.0309334353498015</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.054397293616435</v>
+        <v>0.0543972939508979</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0314168450358414</v>
+        <v>0.0314168456999011</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.989478534328803</v>
+        <v>0.989478534269112</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.01470814674433</v>
+        <v>1.01470775315428</v>
       </c>
     </row>
     <row r="9">
@@ -1911,46 +1911,46 @@
         <v>82.639</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.02531260684506</v>
+        <v>1.02531260626341</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>79.9029985010319</v>
+        <v>79.9029985066007</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>75.542873667602</v>
+        <v>75.5429311033443</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>75.6172828611737</v>
+        <v>75.6172820981459</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>80.5988334175315</v>
+        <v>80.5988334632545</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>80.5988334175315</v>
+        <v>80.5988334632545</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>80.5988334175315</v>
+        <v>80.5988334632545</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>80.5988334175315</v>
+        <v>80.5988334632545</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0579009056523437</v>
+        <v>0.0579009061131429</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.0906520379710996</v>
+        <v>0.0906520378457449</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0596099891469504</v>
+        <v>0.0596099896352178</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>1.00870849567042</v>
+        <v>1.00870849617235</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1.06692834816129</v>
+        <v>1.06692753757454</v>
       </c>
     </row>
     <row r="10">
@@ -1970,46 +1970,46 @@
         <v>82.172</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.02390211539001</v>
+        <v>1.02390211642409</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>80.3342544749721</v>
+        <v>80.3342544305464</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>76.11960419322</v>
+        <v>76.1196912961792</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>76.0786567572683</v>
+        <v>76.0786556018845</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>80.2537652426865</v>
+        <v>80.253765161635</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>80.2537652426865</v>
+        <v>80.253765161635</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>80.2537652426865</v>
+        <v>80.253765161635</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>80.2537652426865</v>
+        <v>80.253765161635</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>-0.00429049585849143</v>
+        <v>-0.00429049743572234</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.150933712743745</v>
+        <v>0.150933711705155</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>-0.00428130483052314</v>
+        <v>-0.00428130640100144</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>0.998998070837756</v>
+        <v>0.998998070381285</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.05431138395009</v>
+        <v>1.05431017644791</v>
       </c>
     </row>
     <row r="11">
@@ -2029,46 +2029,46 @@
         <v>76.665</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.990382882794109</v>
+        <v>0.990382882533831</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>76.7108775752521</v>
+        <v>76.7108776478403</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>76.6937213513691</v>
+        <v>76.6938396181705</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>76.4852765083104</v>
+        <v>76.485274894108</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>77.4094558093629</v>
+        <v>77.4094558297065</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>77.4094558093629</v>
+        <v>77.4094558297065</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>77.4094558093629</v>
+        <v>77.4094558297065</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>77.4094558093629</v>
+        <v>77.4094558297065</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>-0.0360847386080561</v>
+        <v>-0.0360847373353102</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.0496524463418817</v>
+        <v>0.0496524471817579</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>-0.035441445329356</v>
+        <v>-0.0354414441017181</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.00910663853931</v>
+        <v>1.00910663784963</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.0093323735683</v>
+        <v>1.00933081737854</v>
       </c>
     </row>
     <row r="12">
@@ -2088,46 +2088,46 @@
         <v>71.122</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.969628302158772</v>
+        <v>0.969628298937737</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>75.1633878154438</v>
+        <v>75.1633879364653</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>77.2692697598625</v>
+        <v>77.2694208131378</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>76.8630604212141</v>
+        <v>76.8630582827056</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>73.3497566455668</v>
+        <v>73.3497568892293</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>73.3497566455668</v>
+        <v>73.3497568892293</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>73.3497566455668</v>
+        <v>73.3497568892293</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>73.3497566455668</v>
+        <v>73.3497568892293</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.053869754345424</v>
+        <v>-0.053869751286302</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.0356915659000763</v>
+        <v>-0.0356915627994039</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.0524444865468889</v>
+        <v>-0.052444483648201</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.975870816595837</v>
+        <v>0.975870818266348</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.949274619438274</v>
+        <v>0.949272766863525</v>
       </c>
     </row>
     <row r="13">
@@ -2147,46 +2147,46 @@
         <v>79.78</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.01150604590125</v>
+        <v>1.01150604883633</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>78.0508372049294</v>
+        <v>78.0508369406834</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>77.8507413705496</v>
+        <v>77.8509268850327</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>77.2425476993985</v>
+        <v>77.2425449802446</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>78.8724895152912</v>
+        <v>78.8724892864274</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>78.8724895152912</v>
+        <v>78.8724892864274</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>78.8724895152912</v>
+        <v>78.8724892864274</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>78.8724895152912</v>
+        <v>78.8724892864274</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.0725933048376261</v>
+        <v>0.0725932986140052</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>-0.0214189688490556</v>
+        <v>-0.0214189722437373</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.0752931314606924</v>
+        <v>0.0752931247684756</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.01052714281853</v>
+        <v>1.01052714330749</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.01312444977085</v>
+        <v>1.01312203261116</v>
       </c>
     </row>
     <row r="14">
@@ -2206,46 +2206,46 @@
         <v>81.632</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1.01943730818394</v>
+        <v>1.01943731511912</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>78.7362295526816</v>
+        <v>78.7362292947248</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>78.4401784395836</v>
+        <v>78.4404000478547</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>77.6367110274043</v>
+        <v>77.636707692325</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>80.0755469165848</v>
+        <v>80.0755463718349</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>80.0755469165848</v>
+        <v>80.0755463718349</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>80.0755469165848</v>
+        <v>80.0755463718349</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>80.0755469165848</v>
+        <v>80.0755463718349</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.0151380338204363</v>
+        <v>0.0151380299191803</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>-0.00222068491818173</v>
+        <v>-0.00222069069832598</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.0152531942212926</v>
+        <v>0.01525319026053</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1.01701017906893</v>
+        <v>1.0170101754822</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.0208486073022</v>
+        <v>1.02084571627609</v>
       </c>
     </row>
     <row r="15">
@@ -2265,46 +2265,46 @@
         <v>71.358</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.00259035141128</v>
+        <v>1.00259034250185</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.254717985670919</v>
+        <v>0.254717990510303</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>76.3195136724585</v>
+        <v>76.3195141575469</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>79.0402618157079</v>
+        <v>79.040520992104</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>78.0666727988522</v>
+        <v>78.0666688460776</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>71.1736352734236</v>
+        <v>71.1736359059017</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>75.0087658921488</v>
+        <v>75.0087663898772</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>75.0087658921488</v>
+        <v>75.0087663898772</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>75.0087658921488</v>
+        <v>75.0087663898772</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.0653655402575035</v>
+        <v>-0.065365526818952</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.0310128768134769</v>
+        <v>-0.0310128706383187</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.0632750099067581</v>
+        <v>-0.0632749973185309</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.982825522369875</v>
+        <v>0.982825522644655</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.948994400689625</v>
+        <v>0.948991295203766</v>
       </c>
     </row>
     <row r="16">
@@ -2324,46 +2324,46 @@
         <v>75.162</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.977209622970903</v>
+        <v>0.977209613760064</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>75.2224713594378</v>
+        <v>75.2224718488128</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>79.6546944529643</v>
+        <v>79.6549923747332</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>78.5657495868083</v>
+        <v>78.5657450620309</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>76.9149200265683</v>
+        <v>76.9149207515417</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>76.9149200265683</v>
+        <v>76.9149207515417</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>76.9149200265683</v>
+        <v>76.9149207515417</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>76.9149200265683</v>
+        <v>76.9149207515417</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0250948909748593</v>
+        <v>0.0250948937649101</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.0486049789943925</v>
+        <v>0.0486049853947899</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0254124182920203</v>
+        <v>0.0254124211529732</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1.02249924306586</v>
+        <v>1.02249924605151</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>0.965604357091424</v>
+        <v>0.965600754685896</v>
       </c>
     </row>
     <row r="17">
@@ -2383,46 +2383,46 @@
         <v>75.163</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.997104270936833</v>
+        <v>0.997104282232296</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>76.8807130606639</v>
+        <v>76.8807122831204</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>80.284659620442</v>
+        <v>80.2849970060687</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>79.1519684298054</v>
+        <v>79.1519634484322</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>75.3812837742439</v>
+        <v>75.3812829203046</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>75.3812837742439</v>
+        <v>75.3812829203046</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>75.3812837742439</v>
+        <v>75.3812829203046</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>75.3812837742439</v>
+        <v>75.3812829203046</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.0201408578483848</v>
+        <v>-0.0201408786023047</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>-0.0442639222180308</v>
+        <v>-0.0442639302716108</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>-0.0199393856457846</v>
+        <v>-0.0199394059858838</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.980496678208007</v>
+        <v>0.980496677017065</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>0.93892512131982</v>
+        <v>0.938921164991842</v>
       </c>
     </row>
     <row r="18">
@@ -2442,46 +2442,46 @@
         <v>81.025</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.01284566859542</v>
+        <v>1.01284568747017</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>79.0447919513544</v>
+        <v>79.0447904568666</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>80.929628228214</v>
+        <v>80.9300051516723</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>79.8351022185751</v>
+        <v>79.8350969919765</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>79.9973801658872</v>
+        <v>79.9973786751067</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>79.9973801658872</v>
+        <v>79.9973786751067</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>79.9973801658872</v>
+        <v>79.9973786751067</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>79.9973801658872</v>
+        <v>79.9973786751067</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.0594348678162445</v>
+        <v>0.0594348605091448</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>-0.000976162557828286</v>
+        <v>-0.000976174378695016</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.061236638068779</v>
+        <v>0.0612366303142171</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>1.01205124576859</v>
+        <v>1.01205124604334</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>0.988480756890443</v>
+        <v>0.988476134718912</v>
       </c>
     </row>
     <row r="19">
@@ -2501,46 +2501,46 @@
         <v>81.906</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.01502277348035</v>
+        <v>1.01502276857956</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>81.269802846093</v>
+        <v>81.2698051018931</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>81.5860065764495</v>
+        <v>81.5864222558022</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>80.6060704205712</v>
+        <v>80.6060652767181</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>80.6937559825948</v>
+        <v>80.693756372205</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>80.6937559825948</v>
+        <v>80.693756372205</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>80.6937559825948</v>
+        <v>80.693756372205</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>80.6937559825948</v>
+        <v>80.693756372205</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.00866731286914931</v>
+        <v>0.00866733633277182</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0757910095284084</v>
+        <v>0.0757910075840817</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.00870498277898091</v>
+        <v>0.00870500644685412</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.992911920008111</v>
+        <v>0.99291189724196</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.989063681000019</v>
+        <v>0.989058646538042</v>
       </c>
     </row>
     <row r="20">
@@ -2560,46 +2560,46 @@
         <v>79.225</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.985700625346588</v>
+        <v>0.985700546699761</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>78.6352049596182</v>
+        <v>78.6352066412379</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>82.2496183102784</v>
+        <v>82.2500708711688</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>81.4566038929839</v>
+        <v>81.4565992951269</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>80.3743022605299</v>
+        <v>80.3743086734145</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>80.3743022605299</v>
+        <v>80.3743086734145</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>80.3743022605299</v>
+        <v>80.3743086734145</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>80.3743022605299</v>
+        <v>80.3743086734145</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.00396669761124303</v>
+        <v>-0.00396662265175439</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0449767383593014</v>
+        <v>0.044976811886053</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.00395884065842533</v>
+        <v>-0.00395876599568656</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>1.0221160140907</v>
+        <v>1.022116073785</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>0.9771996990591</v>
+        <v>0.977194400224987</v>
       </c>
     </row>
     <row r="21">
@@ -2619,46 +2619,46 @@
         <v>72.614</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.983783088442959</v>
+        <v>0.983783185071159</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.90040322044932</v>
+        <v>0.900403201055685</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>76.1475381170043</v>
+        <v>76.1475356632484</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>82.9157294182097</v>
+        <v>82.9162156343051</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>82.3788719208138</v>
+        <v>82.3788684951504</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>73.8109862357227</v>
+        <v>73.8109789859314</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>74.0436992783514</v>
+        <v>74.0436925515442</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>74.0436992783514</v>
+        <v>74.0436925515442</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>74.0436992783514</v>
+        <v>74.0436925515442</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0820390517711422</v>
+        <v>-0.0820392224080429</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>-0.0177442520068822</v>
+        <v>-0.0177443301167296</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.0787640179028626</v>
+        <v>-0.0787641750997019</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>0.972371544889341</v>
+        <v>0.972371487883624</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>0.892999432048537</v>
+        <v>0.892994114421569</v>
       </c>
     </row>
     <row r="22">
@@ -2678,46 +2678,46 @@
         <v>81.115</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.0062961818815</v>
+        <v>1.00629617984542</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>81.0764566792485</v>
+        <v>81.0764545967071</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>83.5784338162212</v>
+        <v>83.5789488303708</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>83.359632280899</v>
+        <v>83.3596308716275</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>80.6074806408756</v>
+        <v>80.607480803972</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>80.6074806408756</v>
+        <v>80.607480803972</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>80.6074806408756</v>
+        <v>80.607480803972</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>80.6074806408756</v>
+        <v>80.607480803972</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.0849360074293449</v>
+        <v>0.0849361003018415</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>0.00762650568960144</v>
+        <v>0.00762652650586237</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.088647399123712</v>
+        <v>0.0886475002291185</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>0.994215632286099</v>
+        <v>0.994215659835301</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>0.964453112607034</v>
+        <v>0.964447171590664</v>
       </c>
     </row>
     <row r="23">
@@ -2737,46 +2737,46 @@
         <v>93.59</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.02578151049948</v>
+        <v>1.02578150971825</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.85555034628409</v>
+        <v>0.855551571108367</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>88.3358927822563</v>
+        <v>88.3359003019614</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>84.2262804014535</v>
+        <v>84.2268174175984</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>84.3439668868653</v>
+        <v>84.3439685396788</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>91.2377529152661</v>
+        <v>91.2377529847523</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>90.8185802239208</v>
+        <v>90.8185849238482</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>90.8185802239208</v>
+        <v>90.8185849238482</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>90.8185802239208</v>
+        <v>90.8185849238482</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.119272435563184</v>
+        <v>0.119272485290567</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.125472214275289</v>
+        <v>0.125472267085223</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.126676823315419</v>
+        <v>0.12667687934211</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>1.02810508122428</v>
+        <v>1.02810504691071</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.07826891786086</v>
+        <v>1.07826209879886</v>
       </c>
     </row>
     <row r="24">
@@ -2796,46 +2796,46 @@
         <v>88.207</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.992138316168067</v>
+        <v>0.992138183242569</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>91.0216231767187</v>
+        <v>91.0216266334732</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>84.8459612253122</v>
+        <v>84.8465111867044</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>85.2631968941385</v>
+        <v>85.263202864087</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>88.9059504733994</v>
+        <v>88.9059623849132</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>88.9059504733994</v>
+        <v>88.9059623849132</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>88.9059504733994</v>
+        <v>88.9059623849132</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>88.9059504733994</v>
+        <v>88.9059623849132</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.0212848179517566</v>
+        <v>-0.0212847357236742</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0.106148955237142</v>
+        <v>0.106149015180529</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.0210598948563799</v>
+        <v>-0.021059814360009</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>0.976756372502699</v>
+        <v>0.976756466272798</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.04785129650786</v>
+        <v>1.04784464489384</v>
       </c>
     </row>
     <row r="25">
@@ -2855,46 +2855,46 @@
         <v>89.865</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.974843360716823</v>
+        <v>0.974843502919925</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>90.5880883969661</v>
+        <v>90.5880874550254</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>85.4282885265923</v>
+        <v>85.4288397830965</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>86.0810165248297</v>
+        <v>86.0810282915554</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>92.1840406585119</v>
+        <v>92.1840272113724</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>92.1840406585119</v>
+        <v>92.1840272113724</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>92.1840406585119</v>
+        <v>92.1840272113724</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>92.1840406585119</v>
+        <v>92.1840272113724</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.0362079460310631</v>
+        <v>0.0362076661794971</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.244995071247936</v>
+        <v>0.244995002743822</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.0368714373746373</v>
+        <v>0.0368711472045824</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.01761768340394</v>
+        <v>1.0176175455425</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.07908097245582</v>
+        <v>1.07907385193838</v>
       </c>
     </row>
     <row r="26">
@@ -2914,46 +2914,46 @@
         <v>88.789</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.999866285621895</v>
+        <v>0.999866203553702</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>89.7906828466592</v>
+        <v>89.7906759868411</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>85.9666120373687</v>
+        <v>85.9671500091811</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>86.7793337689462</v>
+        <v>86.7793530663915</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>88.8008739536359</v>
+        <v>88.8008812423383</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>88.8008739536359</v>
+        <v>88.8008812423383</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>88.8008739536359</v>
+        <v>88.8008812423383</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>88.8008739536359</v>
+        <v>88.8008812423383</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>-0.0373905289999283</v>
+        <v>-0.0373903010479969</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.101645569959738</v>
+        <v>0.101645658152893</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>-0.0367001346513836</v>
+        <v>-0.0366999150652937</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.988976485514498</v>
+        <v>0.988976642244593</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.03296933366451</v>
+        <v>1.03296295425467</v>
       </c>
     </row>
     <row r="27">
@@ -2973,46 +2973,46 @@
         <v>91.875</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.03546715246575</v>
+        <v>1.03546735337987</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>88.6021913607896</v>
+        <v>88.602188305438</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>86.4585038347988</v>
+        <v>86.4590106595076</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>87.3705717371636</v>
+        <v>87.370600427502</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>88.7280680813667</v>
+        <v>88.7280508652549</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>88.7280680813667</v>
+        <v>88.7280508652549</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>88.7280680813667</v>
+        <v>88.7280508652549</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>88.7280680813667</v>
+        <v>88.7280508652549</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>-0.000820214163575699</v>
+        <v>-0.000820490275073497</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>-0.0230185512413844</v>
+        <v>-0.0230187913668352</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>-0.000819877879886466</v>
+        <v>-0.000820153764968468</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>1.00142069534222</v>
+        <v>1.00142053556717</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.02625032987969</v>
+        <v>1.0262441148521</v>
       </c>
     </row>
     <row r="28">
@@ -3032,46 +3032,46 @@
         <v>87.797</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.992538901177367</v>
+        <v>0.992538739683597</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>88.3289590738522</v>
+        <v>88.3289631927754</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>86.9033074097377</v>
+        <v>86.9037616106459</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>87.8772612410812</v>
+        <v>87.877301254673</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>88.4569863164594</v>
+        <v>88.4570007090988</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>88.4569863164594</v>
+        <v>88.4570007090988</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>88.4569863164594</v>
+        <v>88.4570007090988</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>88.4569863164594</v>
+        <v>88.4570007090988</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.00305987406597334</v>
+        <v>-0.00305951732588501</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.00504987747782182</v>
+        <v>-0.00504984889394311</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00305519742251958</v>
+        <v>-0.00305484177227922</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00144943678664</v>
+        <v>1.00144955303103</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.01787824828572</v>
+        <v>1.01787309397966</v>
       </c>
     </row>
     <row r="29">
@@ -3091,46 +3091,46 @@
         <v>83.817</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.972430425249531</v>
+        <v>0.972430305512795</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>85.6674868541571</v>
+        <v>85.6675099189846</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>87.3017847306945</v>
+        <v>87.3021608892946</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>88.3287205740192</v>
+        <v>88.3287736798798</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>86.1933129853399</v>
+        <v>86.1933235984459</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>86.1933129853399</v>
+        <v>86.1933235984459</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>86.1933129853399</v>
+        <v>86.1933235984459</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>86.1933129853399</v>
+        <v>86.1933235984459</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>-0.0259238044559657</v>
+        <v>-0.0259238440323032</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>-0.064986603216539</v>
+        <v>-0.0649863516939889</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>-0.025590667570576</v>
+        <v>-0.0255907061341279</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>1.00613798945775</v>
+        <v>1.00613784245578</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.987302988721549</v>
+        <v>0.987298856299161</v>
       </c>
     </row>
     <row r="30">
@@ -3150,46 +3150,46 @@
         <v>81.62</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.996747424258214</v>
+        <v>0.996747182495547</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>82.3081694823798</v>
+        <v>82.3081622385862</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>87.655668815495</v>
+        <v>87.6559372965888</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>88.7571666546746</v>
+        <v>88.7572343323696</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>81.8863415280377</v>
+        <v>81.8863613897044</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>81.8863415280377</v>
+        <v>81.8863613897044</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>81.8863415280377</v>
+        <v>81.8863613897044</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>81.8863415280377</v>
+        <v>81.8863613897044</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>-0.0512603922424904</v>
+        <v>-0.0512602728223009</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>-0.0778655898049874</v>
+        <v>-0.0778654418278143</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>-0.0499687424479754</v>
+        <v>-0.0499686289950558</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.994875017182439</v>
+        <v>0.994875346048195</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.934181926104504</v>
+        <v>0.934179291388298</v>
       </c>
     </row>
     <row r="31">
@@ -3209,46 +3209,46 @@
         <v>85.937</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1.03981268241418</v>
+        <v>1.03981367667384</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>83.5398843396373</v>
+        <v>83.5398158039233</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>87.9659998871245</v>
+        <v>87.9661266103568</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>89.1841393638013</v>
+        <v>89.1842225909823</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>82.6466165044998</v>
+        <v>82.6465374786141</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>82.6466165044998</v>
+        <v>82.6465374786141</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>82.6466165044998</v>
+        <v>82.6465374786141</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>82.6466165044998</v>
+        <v>82.6465374786141</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.00924167895254638</v>
+        <v>0.00924048021026338</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0685403357513658</v>
+        <v>-0.0685410456708492</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.00928451512517259</v>
+        <v>0.00928330525387389</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.989307289060806</v>
+        <v>0.989307154717628</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.939529097725822</v>
+        <v>0.939526845881191</v>
       </c>
     </row>
     <row r="32">
@@ -3268,46 +3268,46 @@
         <v>94.097</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.989402097660021</v>
+        <v>0.989401771277558</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>88.6831179111276</v>
+        <v>88.6831418018596</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>88.230212339013</v>
+        <v>88.2301586234852</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>89.5968244565196</v>
+        <v>89.5969234698447</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>95.1049125755277</v>
+        <v>95.1049439486023</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>88.6831179111276</v>
+        <v>88.6831418018596</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>88.6831179111276</v>
+        <v>88.6831418018596</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>88.6831179111276</v>
+        <v>88.6831418018596</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.0704956574597109</v>
+        <v>0.0704968830447061</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.00255640175055483</v>
+        <v>0.00255650870985846</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.0730399097015557</v>
+        <v>0.0730412248039742</v>
       </c>
       <c r="R32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.00513322545767</v>
+        <v>1.00513410817165</v>
       </c>
     </row>
     <row r="33">
@@ -3327,46 +3327,46 @@
         <v>88.379</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.974892283880907</v>
+        <v>0.974891373639551</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.399989714514293</v>
+        <v>0.399943300557646</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>93.3154597281752</v>
+        <v>93.3156188479679</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>88.4424159499768</v>
+        <v>88.442138385653</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>89.9497200736535</v>
+        <v>89.9498335575218</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>90.6551436105083</v>
+        <v>90.6552282538471</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>92.2513606437518</v>
+        <v>92.2516134529827</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>92.2513606437518</v>
+        <v>92.2516134529827</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>92.2513606437518</v>
+        <v>92.2516134529827</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.0394474890834582</v>
+        <v>0.0394499601244243</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.0702844275105463</v>
+        <v>0.0702872287737839</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.0402358737116133</v>
+        <v>0.0402384441802475</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.988596754626478</v>
+        <v>0.988597778077015</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>1.04306694534362</v>
+        <v>1.04307307734599</v>
       </c>
     </row>
     <row r="34">
@@ -3386,46 +3386,46 @@
         <v>95.958</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.998747638099274</v>
+        <v>0.998747220837207</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>95.9204055824935</v>
+        <v>95.9204579026737</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>88.5970035648148</v>
+        <v>88.5964540610259</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>90.1927558233003</v>
+        <v>90.1928805342384</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>96.0783248335071</v>
+        <v>96.0783649736342</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>96.0783248335071</v>
+        <v>96.0783649736342</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>96.0783248335071</v>
+        <v>96.0783649736342</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>96.0783248335071</v>
+        <v>96.0783649736342</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>0.0406467101604059</v>
+        <v>0.0406443875104864</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0.173313192904216</v>
+        <v>0.173313398508316</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>0.0414840947932882</v>
+        <v>0.0414816757931484</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.00164635720684</v>
+        <v>1.00164622932806</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>1.08444214778911</v>
+        <v>1.08444932691612</v>
       </c>
     </row>
     <row r="35">
@@ -3445,46 +3445,46 @@
         <v>99.608</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1.0355858764581</v>
+        <v>1.03558793496551</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>95.5363684344069</v>
+        <v>95.5361729882089</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>88.6907486187593</v>
+        <v>88.6898747356868</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>90.2873695164072</v>
+        <v>90.2875009796969</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>96.1851665461857</v>
+        <v>96.1849753524962</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>96.1851665461857</v>
+        <v>96.1849753524962</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>96.1851665461857</v>
+        <v>96.1849753524962</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>96.1851665461857</v>
+        <v>96.1849753524962</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.00111140937792971</v>
+        <v>0.00110900382369064</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.163812514223722</v>
+        <v>0.163811313660725</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.00111202722220383</v>
+        <v>0.00110961899581952</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.00679111130568</v>
+        <v>1.00679116971084</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>1.08450056002618</v>
+        <v>1.08450909012045</v>
       </c>
     </row>
     <row r="36">
@@ -3504,46 +3504,46 @@
         <v>90.0095</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.986450593368895</v>
+        <v>0.986452128016395</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>91.5034040195123</v>
+        <v>91.5034437398962</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>88.7251003728356</v>
+        <v>88.7238456900386</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>90.224426808973</v>
+        <v>90.2245588957964</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>91.2458268108516</v>
+        <v>91.2456848575059</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>91.2458268108516</v>
+        <v>91.2456848575059</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>91.2458268108516</v>
+        <v>91.2456848575059</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>91.2458268108516</v>
+        <v>91.2456848575059</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0527178940388836</v>
+        <v>-0.0527174619954804</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0.0288973703235402</v>
+        <v>0.0288954924643019</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.051352406121398</v>
+        <v>-0.0513519962643746</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>0.997185053261999</v>
+        <v>0.997183069053411</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>1.02841052224707</v>
+        <v>1.02842346550529</v>
       </c>
     </row>
     <row r="37">
@@ -3563,46 +3563,46 @@
         <v>86.652</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.980719123893401</v>
+        <v>0.980713019609596</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>89.1069758926866</v>
+        <v>89.1072106793643</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>88.7061920992738</v>
+        <v>88.7044966423701</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>90.0242823421451</v>
+        <v>90.0244056563002</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>88.3555728535162</v>
+        <v>88.3561228079694</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>88.3555728535162</v>
+        <v>88.3561228079694</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>88.3555728535162</v>
+        <v>88.3561228079694</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>88.3555728535162</v>
+        <v>88.3561228079694</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>-0.032187984054237</v>
+        <v>-0.032180204015763</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.042230139079249</v>
+        <v>-0.0422268023203588</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>-0.031675464603184</v>
+        <v>-0.0316679309717375</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>0.991567405002328</v>
+        <v>0.991570964171491</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.996047409572432</v>
+        <v>0.99607264741262</v>
       </c>
     </row>
     <row r="38">
@@ -3622,46 +3622,46 @@
         <v>91.424</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.0035376322818</v>
+        <v>1.00354013943448</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>91.0751233106311</v>
+        <v>91.07509893998</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>88.6417325243275</v>
+        <v>88.6395334604495</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>89.7123977570804</v>
+        <v>89.7124982647801</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>91.1017156298605</v>
+        <v>91.1014880296863</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>91.1017156298605</v>
+        <v>91.1014880296863</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>91.1017156298605</v>
+        <v>91.1014880296863</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>91.1017156298605</v>
+        <v>91.1014880296863</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0306073626862079</v>
+        <v>0.0305986400617561</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.0517974185360799</v>
+        <v>-0.0518001835825749</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0310805836876529</v>
+        <v>0.0310715899981662</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00029198224787</v>
+        <v>1.00028975087607</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.02775197455508</v>
+        <v>1.0277749044148</v>
       </c>
     </row>
     <row r="39">
@@ -3681,46 +3681,46 @@
         <v>95.267</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1.02616195057695</v>
+        <v>1.02616520534618</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>91.5257464660411</v>
+        <v>91.525315804557</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>88.5392112372219</v>
+        <v>88.5364442783986</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>89.3058911474925</v>
+        <v>89.3059523105662</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>92.838172324005</v>
+        <v>92.8378778618413</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>92.838172324005</v>
+        <v>92.8378778618413</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>92.838172324005</v>
+        <v>92.8378778618413</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>92.838172324005</v>
+        <v>92.8378778618413</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.018881258444452</v>
+        <v>0.0188805849718813</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>-0.0347974052794668</v>
+        <v>-0.0347985480932808</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.0190606365877857</v>
+        <v>0.0190599502786302</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.01433941714369</v>
+        <v>1.01434097272155</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>1.04855431877821</v>
+        <v>1.04858376252289</v>
       </c>
     </row>
     <row r="40">
@@ -3740,46 +3740,46 @@
         <v>85.922</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.98442935075714</v>
+        <v>0.984432038164209</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>88.3558688997179</v>
+        <v>88.3560914484994</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>88.407655316623</v>
+        <v>88.4042559519449</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>88.828827196459</v>
+        <v>88.8288283318132</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>87.2810221819535</v>
+        <v>87.2807839129548</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>87.2810221819535</v>
+        <v>87.2807839129548</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>87.2810221819535</v>
+        <v>87.2807839129548</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>87.2810221819535</v>
+        <v>87.2807839129548</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>-0.0617248419316777</v>
+        <v>-0.0617244000575357</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>-0.0434519009523253</v>
+        <v>-0.0434530241155278</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>-0.0598584612658799</v>
+        <v>-0.0598580458415523</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.987835027472998</v>
+        <v>0.987829842652429</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.987256384861304</v>
+        <v>0.98729165211683</v>
       </c>
     </row>
     <row r="41">
@@ -3799,46 +3799,46 @@
         <v>84.925</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.987266560755259</v>
+        <v>0.98725269374366</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>85.727283879576</v>
+        <v>85.7276258682371</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>88.2587786918761</v>
+        <v>88.2546837328057</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>88.3229319929403</v>
+        <v>88.3228464944321</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>86.0203347057884</v>
+        <v>86.0215429526605</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>86.0203347057884</v>
+        <v>86.0215429526605</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>86.0203347057884</v>
+        <v>86.0215429526605</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>86.0203347057884</v>
+        <v>86.0215429526605</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>-0.0145493346109219</v>
+        <v>-0.0145325587386564</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>-0.0264300040428617</v>
+        <v>-0.0264223890899206</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>-0.014444004488592</v>
+        <v>-0.0144274707884174</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>1.00341840792045</v>
+        <v>1.00342849905671</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.974637718544663</v>
+        <v>0.974696631547554</v>
       </c>
     </row>
     <row r="42">
@@ -3858,46 +3858,46 @@
         <v>86.89</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.01025731770306</v>
+        <v>1.01026863575447</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>86.3529540357628</v>
+        <v>86.3528304751809</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>88.1035911466176</v>
+        <v>88.0987407026739</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>87.8221926008238</v>
+        <v>87.8219867422397</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>86.0077907651832</v>
+        <v>86.0068272188916</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>86.0077907651832</v>
+        <v>86.0068272188916</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>86.0077907651832</v>
+        <v>86.0068272188916</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>86.0077907651832</v>
+        <v>86.0068272188916</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>-0.000145835927620885</v>
+        <v>-0.000171084964533668</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>-0.0559146974286795</v>
+        <v>-0.0559229154317938</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>-0.000145825294078916</v>
+        <v>-0.000171070330335699</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.996002878252009</v>
+        <v>0.995993145165186</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.9762120890402</v>
+        <v>0.976254899138203</v>
       </c>
     </row>
     <row r="43">
@@ -3917,46 +3917,46 @@
         <v>89.474</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1.01460383172613</v>
+        <v>1.01460342522738</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>88.0256253387488</v>
+        <v>88.0250089469432</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>87.951703436992</v>
+        <v>87.9460442302546</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>87.3490830975615</v>
+        <v>87.3487225013438</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>88.186144386799</v>
+        <v>88.1861797183941</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>88.186144386799</v>
+        <v>88.1861797183941</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>88.186144386799</v>
+        <v>88.1861797183941</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>88.186144386799</v>
+        <v>88.1861797183941</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0250119751088533</v>
+        <v>0.0250235788312081</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>-0.0501089995715388</v>
+        <v>-0.0501056061446139</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0253273988581231</v>
+        <v>0.0253392965416108</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.0018235490794</v>
+        <v>1.00183096569235</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.00266556462974</v>
+        <v>1.00273048651865</v>
       </c>
     </row>
     <row r="44">
@@ -3976,46 +3976,46 @@
         <v>87.112</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.981020216346337</v>
+        <v>0.981025143103763</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>88.562818479769</v>
+        <v>88.5633024147548</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>87.8114164439061</v>
+        <v>87.8049042383258</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>86.917005551427</v>
+        <v>86.9164514002356</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>88.7973545789256</v>
+        <v>88.7969086341614</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>88.7973545789256</v>
+        <v>88.7969086341614</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>88.7973545789256</v>
+        <v>88.7969086341614</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>88.7973545789256</v>
+        <v>88.7969086341614</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.00690700122436927</v>
+        <v>0.0069015785138129</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0173729908182223</v>
+        <v>0.0173706588464955</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0069309095706207</v>
+        <v>0.00692544929055261</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00264824565413</v>
+        <v>1.00263773157772</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.01122790378458</v>
+        <v>1.01129782447166</v>
       </c>
     </row>
     <row r="45">
@@ -4035,46 +4035,46 @@
         <v>85.925</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.996006735620869</v>
+        <v>0.995985750743005</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>86.099886742666</v>
+        <v>86.1002628528569</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>87.6911775738597</v>
+        <v>87.6837807343455</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>86.5435473371404</v>
+        <v>86.5427583534916</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>86.2694969090123</v>
+        <v>86.271314560374</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>86.2694969090123</v>
+        <v>86.271314560374</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>86.2694969090123</v>
+        <v>86.271314560374</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>86.2694969090123</v>
+        <v>86.271314560374</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.0288807772917577</v>
+        <v>-0.028854685995085</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.00289655003175771</v>
+        <v>0.00290359367130799</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.0284677137275128</v>
+        <v>-0.0284423648597136</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.00196992322247</v>
+        <v>1.00198665720463</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.983787643133769</v>
+        <v>0.983891363235684</v>
       </c>
     </row>
     <row r="46">
@@ -4094,46 +4094,46 @@
         <v>83.698</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.01791667062343</v>
+        <v>1.01793663856895</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>82.1909154367643</v>
+        <v>82.1907744031638</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>87.6000504446875</v>
+        <v>87.5917537285189</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>86.2556975745588</v>
+        <v>86.2546305618577</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>82.2248052473083</v>
+        <v>82.2231923174172</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>82.2248052473083</v>
+        <v>82.2231923174172</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>82.2248052473083</v>
+        <v>82.2231923174172</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>82.2248052473083</v>
+        <v>82.2231923174172</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>-0.0480190579462322</v>
+        <v>-0.0480597434712326</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>-0.0439842191529269</v>
+        <v>-0.0439922622868625</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>-0.0468843775218709</v>
+        <v>-0.0469231547425164</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>1.00041233036965</v>
+        <v>1.00039442278636</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>0.938638788789588</v>
+        <v>0.938709282751194</v>
       </c>
     </row>
     <row r="47">
@@ -4153,46 +4153,46 @@
         <v>80.547</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.99939894372727</v>
+        <v>0.999393293246436</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>81.5213788697338</v>
+        <v>81.5215019997493</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>87.5462101238083</v>
+        <v>87.5370204396929</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>86.0790751313991</v>
+        <v>86.0776980071143</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>80.5954423962057</v>
+        <v>80.5958980756721</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>80.5954423962057</v>
+        <v>80.5958980756721</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>80.5954423962057</v>
+        <v>80.5958980756721</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>80.5954423962057</v>
+        <v>80.5958980756721</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>-0.0200149215774988</v>
+        <v>-0.0199896513913356</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>-0.08607590277787</v>
+        <v>-0.0860711016959823</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>-0.0198159526945909</v>
+        <v>-0.0197911829482745</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.988641795730569</v>
+        <v>0.988645892171122</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.920604584507167</v>
+        <v>0.920706435641104</v>
       </c>
     </row>
     <row r="48">
@@ -4212,46 +4212,46 @@
         <v>84.243</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.982137965699148</v>
+        <v>0.982147457716069</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>85.506714023453</v>
+        <v>85.5036576604078</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>87.5344721503927</v>
+        <v>87.524422735832</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>86.0191444137416</v>
+        <v>86.0174334798197</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>85.775118101692</v>
+        <v>85.7742891234505</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>85.775118101692</v>
+        <v>85.7742891234505</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>85.775118101692</v>
+        <v>85.7742891234505</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>85.775118101692</v>
+        <v>85.7742891234505</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.0622868636603341</v>
+        <v>0.0622715451647391</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.0340352084987769</v>
+        <v>-0.034039693016386</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0642676006420211</v>
+        <v>0.0642512977883367</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.00313898249166</v>
+        <v>1.0031651448657</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.979901014931833</v>
+        <v>0.980004054209375</v>
       </c>
     </row>
     <row r="49">
@@ -4271,46 +4271,46 @@
         <v>92.858</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.00170494831643</v>
+        <v>1.00168737444756</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.181180439466808</v>
+        <v>0.178866432947105</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>88.5563801657016</v>
+        <v>88.5504216232361</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>87.5653078337815</v>
+        <v>87.5544642834235</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>86.053951663991</v>
+        <v>86.051900770875</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>92.6999513739718</v>
+        <v>92.7015777264958</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>89.307114218178</v>
+        <v>89.2929241080328</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>89.307114218178</v>
+        <v>89.2929241080328</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>89.307114218178</v>
+        <v>89.2929241080328</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0403521855848499</v>
+        <v>0.0402029464100756</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0352107919716915</v>
+        <v>0.0350244987346777</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0411773972995124</v>
+        <v>0.041022024438093</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.00847746995837</v>
+        <v>1.0083850813038</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.0198915121466</v>
+        <v>1.01985575308852</v>
       </c>
     </row>
     <row r="50">
@@ -4330,46 +4330,46 @@
         <v>89.564</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.0253423123696</v>
+        <v>1.02534720770679</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>88.355352578422</v>
+        <v>88.3529437680694</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>87.6380888870352</v>
+        <v>87.6265549154469</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>86.1603229929914</v>
+        <v>86.1579479493992</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>87.3503403882891</v>
+        <v>87.3499233496834</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>87.3503403882891</v>
+        <v>87.3499233496834</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>87.3503403882891</v>
+        <v>87.3499233496834</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>87.3503403882891</v>
+        <v>87.3499233496834</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0221542178015689</v>
+        <v>-0.0220000883591859</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.0623356312680179</v>
+        <v>0.0623513985260356</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0219106153750362</v>
+        <v>-0.0217598513852969</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.988625338920572</v>
+        <v>0.98864757216218</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.996716627411661</v>
+        <v>0.996843062402368</v>
       </c>
     </row>
     <row r="51">
@@ -4389,46 +4389,46 @@
         <v>86.82</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.985281164933762</v>
+        <v>0.985268678089012</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>87.5310065894602</v>
+        <v>87.530923204774</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>87.7532756522044</v>
+        <v>87.7411910022719</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>86.3313503243581</v>
+        <v>86.3286282011975</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>88.1169792846255</v>
+        <v>88.1180960389329</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>88.1169792846255</v>
+        <v>88.1180960389329</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>88.1169792846255</v>
+        <v>88.1180960389329</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>88.1169792846255</v>
+        <v>88.1180960389329</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.00873830837574197</v>
+        <v>0.00875575617109111</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.0933245933615463</v>
+        <v>0.0933322680541155</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.00877659884241511</v>
+        <v>0.0087941999236143</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00669445854671</v>
+        <v>1.00670817595269</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>1.00414461602394</v>
+        <v>1.00429564532183</v>
       </c>
     </row>
     <row r="52">
@@ -4448,46 +4448,46 @@
         <v>85.782</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.984957025946473</v>
+        <v>0.985004947820221</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>87.5467132904612</v>
+        <v>87.5436713810714</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>87.9111486285279</v>
+        <v>87.8986960195398</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>86.5660756686827</v>
+        <v>86.5629545890761</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>87.0921245701757</v>
+        <v>87.0878874160301</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>87.0921245701757</v>
+        <v>87.0878874160301</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>87.0921245701757</v>
+        <v>87.0878874160301</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>87.0921245701757</v>
+        <v>87.0878874160301</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>-0.0116987802627558</v>
+        <v>-0.0117601063128446</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.0153541784334501</v>
+        <v>0.0153145925894993</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.0116306156063232</v>
+        <v>-0.0116912265381632</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>0.994807472454422</v>
+        <v>0.994793638902151</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.990683501795511</v>
+        <v>0.990775646963757</v>
       </c>
     </row>
     <row r="53">
@@ -4507,46 +4507,46 @@
         <v>87.96</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.00524329944529</v>
+        <v>1.00523390428944</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>87.3316460387752</v>
+        <v>87.3364205677957</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>88.112215630015</v>
+        <v>88.0996290085397</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>86.8724691813583</v>
+        <v>86.8688875150301</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>87.5012049804637</v>
+        <v>87.5020227875973</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>87.5012049804637</v>
+        <v>87.5020227875973</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>87.5012049804637</v>
+        <v>87.5020227875973</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>87.5012049804637</v>
+        <v>87.5020227875973</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0046861029564282</v>
+        <v>0.00474410173889329</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.0202213368276847</v>
+        <v>-0.0200564752283025</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.00469709990779266</v>
+        <v>0.00475537280619576</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.0019415521106</v>
+        <v>1.00189614159505</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.993065539832559</v>
+        <v>0.993216699914997</v>
       </c>
     </row>
     <row r="54">
@@ -4566,46 +4566,46 @@
         <v>94.997</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.02975825400272</v>
+        <v>1.02967289316395</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>85.9869126932651</v>
+        <v>85.9957257927148</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>88.3564725806384</v>
+        <v>88.3440422551837</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>87.2611312622853</v>
+        <v>87.2570120451894</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>92.2517490204542</v>
+        <v>92.2593967760925</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>85.9869126932651</v>
+        <v>85.9957257927148</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>85.9869126932651</v>
+        <v>85.9957257927148</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>85.9869126932651</v>
+        <v>85.9957257927148</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0174574577860726</v>
+        <v>-0.0173643157351966</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.0156087278992079</v>
+        <v>-0.015503133889968</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0173059592440666</v>
+        <v>-0.0172144248429423</v>
       </c>
       <c r="R54" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.973181818850783</v>
+        <v>0.973418507886636</v>
       </c>
     </row>
     <row r="55">
@@ -4625,46 +4625,46 @@
         <v>76.449</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.975514719226065</v>
+        <v>0.975538832711957</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>83.0807294080992</v>
+        <v>83.0779735903952</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>88.6435335227149</v>
+        <v>88.6316145414955</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>87.7458059903597</v>
+        <v>87.7410789220467</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>78.3678590320519</v>
+        <v>78.3659219259114</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>83.0807294080992</v>
+        <v>83.0779735903952</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>83.0807294080992</v>
+        <v>83.0779735903952</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>83.0807294080992</v>
+        <v>83.0779735903952</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.0343823281314672</v>
+        <v>-0.0345179872873536</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0571541366648393</v>
+        <v>-0.0571973598511571</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0337979722045948</v>
+        <v>-0.0339290374657989</v>
       </c>
       <c r="R55" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.937245235004196</v>
+        <v>0.937340180703803</v>
       </c>
     </row>
     <row r="56">
@@ -4684,46 +4684,46 @@
         <v>81.448</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.990287732021796</v>
+        <v>0.990424306449998</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>83.1612726445922</v>
+        <v>83.1506321729575</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>88.9715315236315</v>
+        <v>88.9605569517099</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>88.3338663516325</v>
+        <v>88.3285324568321</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>82.2468029909991</v>
+        <v>82.2354615790237</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>82.2468029909991</v>
+        <v>82.2354615790237</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>82.2468029909991</v>
+        <v>82.2354615790237</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>82.2468029909991</v>
+        <v>82.2354615790237</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.0100882590768053</v>
+        <v>-0.0101929925422147</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0556344400034974</v>
+        <v>-0.0557187225569697</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.0100375432791853</v>
+        <v>-0.0101412200485944</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>0.98900365970226</v>
+        <v>0.988993822776594</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.924417075692957</v>
+        <v>0.924403627819723</v>
       </c>
     </row>
     <row r="57">
@@ -4743,46 +4743,46 @@
         <v>88.796</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.00427650538007</v>
+        <v>1.00425154249554</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>88.3600834698856</v>
+        <v>88.3636858343911</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>89.3351228982038</v>
+        <v>89.3256095444674</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>89.0093599492433</v>
+        <v>89.0035014341179</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>88.4178804585247</v>
+        <v>88.4200782797347</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>88.4178804585247</v>
+        <v>88.4200782797347</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>88.4178804585247</v>
+        <v>88.4200782797347</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>88.4178804585247</v>
+        <v>88.4200782797347</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0723496973409278</v>
+        <v>0.072512458610631</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.0104761469086705</v>
+        <v>0.0104918202218698</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0750312138965568</v>
+        <v>0.0752062015821238</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00065410744727</v>
+        <v>1.00063818575257</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.989732566431635</v>
+        <v>0.989862579507147</v>
       </c>
     </row>
     <row r="58">
@@ -4802,46 +4802,46 @@
         <v>96.617</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.03190947377405</v>
+        <v>1.03169615438069</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>91.8592097707297</v>
+        <v>91.8783889167648</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>89.7247610059143</v>
+        <v>89.7173091938004</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>89.7258990695284</v>
+        <v>89.719649284087</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>93.6293371226046</v>
+        <v>93.6486964594703</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>93.6293371226046</v>
+        <v>93.6486964594703</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>93.6293371226046</v>
+        <v>93.6486964594703</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>93.6293371226046</v>
+        <v>93.6486964594703</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0572695483508036</v>
+        <v>0.0574514357989062</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.0888789257570131</v>
+        <v>0.0889924539412841</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0589412077857308</v>
+        <v>0.0591338334172669</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>1.01927000413233</v>
+        <v>1.01926794280545</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.04351726405193</v>
+        <v>1.04381971885913</v>
       </c>
     </row>
     <row r="59">
@@ -4861,46 +4861,46 @@
         <v>88.033</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.970418169708357</v>
+        <v>0.970338858488691</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>93.4408802316494</v>
+        <v>93.428763747032</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>90.130325929721</v>
+        <v>90.1256268167009</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>90.4341386013708</v>
+        <v>90.4277223211504</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>90.7165619399489</v>
+        <v>90.7239767117149</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>90.7165619399489</v>
+        <v>90.7239767117149</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>90.7165619399489</v>
+        <v>90.7239767117149</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>90.7165619399489</v>
+        <v>90.7239767117149</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>-0.0316038233974546</v>
+        <v>-0.031728835489283</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.0919085880233654</v>
+        <v>0.092034058979547</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>-0.0311096422571218</v>
+        <v>-0.0312307576968907</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.970844471017967</v>
+        <v>0.971049739642916</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.00650431477065</v>
+        <v>1.00663906500457</v>
       </c>
     </row>
     <row r="60">
@@ -4920,46 +4920,46 @@
         <v>96.158</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.99519373768435</v>
+        <v>0.995852437355571</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>93.7668967815551</v>
+        <v>93.7419594963467</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>90.5441381126544</v>
+        <v>90.542990447202</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>91.1042506239187</v>
+        <v>91.0981120955962</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>96.6223925642294</v>
+        <v>96.5584823544159</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>96.6223925642294</v>
+        <v>96.5584823544159</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>96.6223925642294</v>
+        <v>96.5584823544159</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>96.6223925642294</v>
+        <v>96.5584823544159</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0630705796645037</v>
+        <v>0.0623271855164305</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.174785998366447</v>
+        <v>0.17417085646961</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0651020111210781</v>
+        <v>0.0643105147522447</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>1.03045313304253</v>
+        <v>1.03004548734848</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.06713029223396</v>
+        <v>1.06643796364029</v>
       </c>
     </row>
     <row r="61">
@@ -4979,46 +4979,46 @@
         <v>91.528</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.00373906064027</v>
+        <v>1.00328677844605</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>93.0730461442715</v>
+        <v>93.0844523637186</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>90.9588843952519</v>
+        <v>90.962202088021</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>91.7078193330132</v>
+        <v>91.7026914296652</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>91.1870461050063</v>
+        <v>91.2281532721522</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>91.1870461050063</v>
+        <v>91.2281532721522</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>91.1870461050063</v>
+        <v>91.2281532721522</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>91.1870461050063</v>
+        <v>91.2281532721522</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0578976727688933</v>
+        <v>-0.0567853119384467</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0313190684069893</v>
+        <v>0.0317583409452942</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0562534865363635</v>
+        <v>-0.0552031157935862</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.979736345618884</v>
+        <v>0.980057903931012</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.00250840488284</v>
+        <v>1.00292375490068</v>
       </c>
     </row>
     <row r="62">
@@ -5038,46 +5038,46 @@
         <v>95.906</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.02969863719356</v>
+        <v>1.02939563635544</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>93.2198120997934</v>
+        <v>93.2634051368845</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>91.3710505270826</v>
+        <v>91.3798234243174</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>92.2440196341969</v>
+        <v>92.2406349968924</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>93.1398727120699</v>
+        <v>93.1672882736843</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>93.1398727120699</v>
+        <v>93.1672882736843</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>93.1398727120699</v>
+        <v>93.1672882736843</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>93.1398727120699</v>
+        <v>93.1672882736843</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.021189522253581</v>
+        <v>0.0210331282918672</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.00522768210880042</v>
+        <v>-0.00514057540559865</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.0214156142837967</v>
+        <v>0.02125588354011</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.999142463539425</v>
+        <v>0.998969404311808</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>1.01935867186361</v>
+        <v>1.01956082625666</v>
       </c>
     </row>
     <row r="63">
@@ -5097,46 +5097,46 @@
         <v>92.486</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.968189397627199</v>
+        <v>0.968144172623584</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>93.8112596129938</v>
+        <v>93.7654802556008</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>91.7772648587846</v>
+        <v>91.7925823607407</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>92.7094225668725</v>
+        <v>92.7087447800249</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>95.5246981909336</v>
+        <v>95.5291604445351</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>95.5246981909336</v>
+        <v>95.5291604445351</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>95.5246981909336</v>
+        <v>95.5291604445351</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>95.5246981909336</v>
+        <v>95.5291604445351</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.0252824629275315</v>
+        <v>0.0250348699531079</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.053001746849352</v>
+        <v>0.0529648711066664</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.0256047749414059</v>
+        <v>0.0253508738379569</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.01826474332621</v>
+        <v>1.01880948280888</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.04083182624711</v>
+        <v>1.04070675415917</v>
       </c>
     </row>
     <row r="64">
@@ -5156,46 +5156,46 @@
         <v>90.384</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.00096736679502</v>
+        <v>1.00250645766</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>92.0653320880057</v>
+        <v>92.0398860925324</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>92.1752612548616</v>
+        <v>92.1983239674713</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>93.1050784358321</v>
+        <v>93.1084560281943</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>90.29665001907</v>
+        <v>90.1580227333096</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>90.29665001907</v>
+        <v>90.1580227333096</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>90.29665001907</v>
+        <v>90.1580227333096</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>90.29665001907</v>
+        <v>90.1580227333096</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.0562844724650912</v>
+        <v>-0.0578676069983946</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0654687011704288</v>
+        <v>-0.0662858349162276</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.0547298057033779</v>
+        <v>-0.0562251116437263</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.980788837352533</v>
+        <v>0.979553827811881</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.979619138473638</v>
+        <v>0.977870517094416</v>
       </c>
     </row>
     <row r="65">
@@ -5215,46 +5215,46 @@
         <v>93.156</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00441788976592</v>
+        <v>1.00256385217747</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>91.83688015498</v>
+        <v>91.8828400574378</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>92.5651157256495</v>
+        <v>92.5972286759919</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>93.4461139239878</v>
+        <v>93.4553060688544</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>92.7462572592271</v>
+        <v>92.9177725664798</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>92.7462572592271</v>
+        <v>92.9177725664798</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>92.7462572592271</v>
+        <v>92.9177725664798</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>92.7462572592271</v>
+        <v>92.9177725664798</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0267669862874838</v>
+        <v>0.0301509972472026</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.0170990422523973</v>
+        <v>0.0185208100101197</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.0271284398661495</v>
+        <v>0.0306101414993711</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.00990209056223</v>
+        <v>1.01126361035853</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.00195690927578</v>
+        <v>1.00346170069095</v>
       </c>
     </row>
     <row r="66">
@@ -5274,46 +5274,46 @@
         <v>96.275</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.02337163268179</v>
+        <v>1.02373251031447</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>94.757079904479</v>
+        <v>94.813276169285</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>92.9457301494622</v>
+        <v>92.9882017295139</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>93.7336135721683</v>
+        <v>93.7500800629845</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>94.0762836543624</v>
+        <v>94.0431206687245</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>94.0762836543624</v>
+        <v>94.0431206687245</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>94.0762836543624</v>
+        <v>94.0431206687245</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>94.0762836543624</v>
+        <v>94.0431206687245</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0142386337238108</v>
+        <v>0.0120384715075136</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.0100538138503503</v>
+        <v>0.00940064277139196</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0143404859068095</v>
+        <v>0.0121112255617151</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.992815352153075</v>
+        <v>0.991877134387959</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>1.01216358732222</v>
+        <v>1.01134465361831</v>
       </c>
     </row>
     <row r="67">
@@ -5333,46 +5333,46 @@
         <v>94.864</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.969242776599726</v>
+        <v>0.969349444340149</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>97.6215503495521</v>
+        <v>97.4957754369288</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>93.3161196180722</v>
+        <v>93.3703487111802</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>93.9651626378781</v>
+        <v>93.9908755040523</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>97.8743430338471</v>
+        <v>97.8635728878716</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>97.8743430338471</v>
+        <v>97.8635728878716</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>97.8743430338471</v>
+        <v>97.8635728878716</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>97.8743430338471</v>
+        <v>97.8635728878716</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.039578460593677</v>
+        <v>0.0398209877877546</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.024597249584783</v>
+        <v>0.0244366477468616</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0403721238972286</v>
+        <v>0.0406244730287604</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00258951720588</v>
+        <v>1.00377244500384</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.04884711703006</v>
+        <v>1.04812260250404</v>
       </c>
     </row>
     <row r="68">
@@ -5392,46 +5392,46 @@
         <v>98.771</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1.00319682410812</v>
+        <v>1.00561138467311</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>97.5627297462889</v>
+        <v>97.5519010638801</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>93.676005819192</v>
+        <v>93.7434345284709</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>94.140059729033</v>
+        <v>94.177255088554</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>98.4562526778443</v>
+        <v>98.2198506355485</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>98.4562526778443</v>
+        <v>98.2198506355485</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>98.4562526778443</v>
+        <v>98.2198506355485</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>98.4562526778443</v>
+        <v>98.2198506355485</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.00592787227987797</v>
+        <v>0.0036339445053057</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.0903644006400135</v>
+        <v>0.0894188632118302</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.00594547688351788</v>
+        <v>0.00364055528695184</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00915844538052</v>
+        <v>1.00684711998827</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.05102957600347</v>
+        <v>1.04775178261383</v>
       </c>
     </row>
     <row r="69">
@@ -5451,46 +5451,46 @@
         <v>94.481</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.0096213775425</v>
+        <v>1.00552643824657</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>94.8969340104778</v>
+        <v>95.0014499693762</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>94.0279593301696</v>
+        <v>94.1100323539762</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>94.2771493555285</v>
+        <v>94.3281449999051</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>93.5806254716737</v>
+        <v>93.9617263219407</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>93.5806254716737</v>
+        <v>93.9617263219407</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>93.5806254716737</v>
+        <v>93.9617263219407</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>93.5806254716737</v>
+        <v>93.9617263219407</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>-0.0507889450368825</v>
+        <v>-0.0443208073294977</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.00899624671769295</v>
+        <v>0.0112352430178413</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>-0.049520747271623</v>
+        <v>-0.0433529911321888</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.986129072002909</v>
+        <v>0.989055707594245</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.995242544221075</v>
+        <v>0.998424120911172</v>
       </c>
     </row>
     <row r="70">
@@ -5510,46 +5510,46 @@
         <v>94.508</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.01430635111233</v>
+        <v>1.01582391370471</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>91.6572033694508</v>
+        <v>91.6317267191912</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>94.3775383826392</v>
+        <v>94.4755131203535</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>94.4168569920041</v>
+        <v>94.4826843992558</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>93.1750056542174</v>
+        <v>93.0358093809086</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>93.1750056542174</v>
+        <v>93.0358093809086</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>93.1750056542174</v>
+        <v>93.0358093809086</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>93.1750056542174</v>
+        <v>93.0358093809086</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>-0.00434386318440928</v>
+        <v>-0.00990306641904748</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>-0.00958028915615161</v>
+        <v>-0.0107111639921461</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>-0.00433444225673696</v>
+        <v>-0.00985419252366182</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.01655955264802</v>
+        <v>1.01532310600258</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.987258274065739</v>
+        <v>0.984761091081762</v>
       </c>
     </row>
     <row r="71">
@@ -5569,46 +5569,46 @@
         <v>86.553</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.971482184569185</v>
+        <v>0.972011903598171</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0.941355768761722</v>
+        <v>0.928582499589673</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>91.3168122953784</v>
+        <v>91.4918911392034</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>94.7300216245737</v>
+        <v>94.8451550689901</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>94.5961254936801</v>
+        <v>94.6781803543667</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>89.0937593862135</v>
+        <v>89.0452058041678</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>89.2241286150735</v>
+        <v>89.2199419550866</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>89.2241286150735</v>
+        <v>89.2199419550866</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>89.2241286150735</v>
+        <v>89.2199419550866</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>-0.0433280028727929</v>
+        <v>-0.0418798870301383</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>-0.0883808171849714</v>
+        <v>-0.0883232716496929</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>-0.0424027560975536</v>
+        <v>-0.041015039813316</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.977083259613401</v>
+        <v>0.975167753602775</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>0.941878056026201</v>
+        <v>0.940690559156008</v>
       </c>
     </row>
     <row r="72">
@@ -5628,46 +5628,46 @@
         <v>96.169</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1.00387409125835</v>
+        <v>1.00693501551466</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>0.568355099410975</v>
+        <v>0.977224881700814</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>92.7706237364321</v>
+        <v>93.5328470959731</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>95.0899361209906</v>
+        <v>95.2233366264361</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>94.845688459088</v>
+        <v>94.9447055579065</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>95.797870308071</v>
+        <v>95.5066598323096</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>94.4911747625974</v>
+        <v>95.4617060137391</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>94.4911747625974</v>
+        <v>95.4617060137391</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>94.4911747625974</v>
+        <v>95.4617060137391</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0573549382067389</v>
+        <v>0.0676206038036652</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>-0.0402724845543421</v>
+        <v>-0.0280813359413845</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0590316344836139</v>
+        <v>0.0699592929772874</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.01854629145379</v>
+        <v>1.02062226242067</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>0.993703210004986</v>
+        <v>1.00250326648643</v>
       </c>
     </row>
     <row r="73">
@@ -5687,46 +5687,46 @@
         <v>94.588</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.015047749916</v>
+        <v>1.00858357643107</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>93.4654269169376</v>
+        <v>94.0225040014406</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>95.4583677537765</v>
+        <v>95.6109204610454</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>95.1694195023659</v>
+        <v>95.2850415105476</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>93.18576392867</v>
+        <v>93.7830063966587</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>93.18576392867</v>
+        <v>93.7830063966587</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>93.18576392867</v>
+        <v>93.7830063966587</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>93.18576392867</v>
+        <v>93.7830063966587</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>-0.0139114789051219</v>
+        <v>-0.017741511801644</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>-0.00421947963067737</v>
+        <v>-0.00190205025256318</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>-0.0138151614392269</v>
+        <v>-0.0175850577910134</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.997007845601388</v>
+        <v>0.997452762960044</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.976192722769276</v>
+        <v>0.980881743888958</v>
       </c>
     </row>
     <row r="74">
@@ -5746,46 +5746,46 @@
         <v>93.383</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.00757573004315</v>
+        <v>1.01048579994282</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>93.5632673272589</v>
+        <v>93.516200803835</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>95.8360281789691</v>
+        <v>96.0089182220391</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>95.5694196691698</v>
+        <v>95.7045547152416</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>92.6808747130112</v>
+        <v>92.4139656443309</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>92.6808747130112</v>
+        <v>92.4139656443309</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>92.6808747130112</v>
+        <v>92.4139656443309</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>92.6808747130112</v>
+        <v>92.4139656443309</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.00543282496729585</v>
+        <v>-0.0147055605565203</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>-0.00530325635868478</v>
+        <v>-0.00668391816780767</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.00541809386297698</v>
+        <v>-0.0145979618795482</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.990569027360264</v>
+        <v>0.988213430934644</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>0.967077585268186</v>
+        <v>0.962556055788545</v>
       </c>
     </row>
     <row r="75">
@@ -5805,46 +5805,46 @@
         <v>93.705</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.97254647663407</v>
+        <v>0.973417727094876</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>94.8377946112152</v>
+        <v>94.670072586757</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>96.2222086752152</v>
+        <v>96.4171991123479</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>96.0378717272871</v>
+        <v>96.2011014993707</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>96.3501511252273</v>
+        <v>96.2639136228375</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>96.3501511252273</v>
+        <v>96.2639136228375</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>96.3501511252273</v>
+        <v>96.2639136228375</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>96.3501511252273</v>
+        <v>96.2639136228375</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>0.0388268258510686</v>
+        <v>0.0408154092773605</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0798665408198784</v>
+        <v>0.0789506416771364</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>0.0395904378716549</v>
+        <v>0.0416598070612375</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1.01594677016913</v>
+        <v>1.01683574325582</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.00132965613421</v>
+        <v>0.998410185206358</v>
       </c>
     </row>
     <row r="76">
@@ -5864,46 +5864,46 @@
         <v>95.89</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>1.0031011206711</v>
+        <v>1.00678921186833</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>97.6554356024809</v>
+        <v>97.0230104892283</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>96.6142285502455</v>
+        <v>96.8333854895415</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>96.5525157197244</v>
+        <v>96.7560852449622</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>95.5935528572106</v>
+        <v>95.2433725646046</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>95.5935528572106</v>
+        <v>95.2433725646046</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>95.5935528572106</v>
+        <v>95.2433725646046</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>95.5935528572106</v>
+        <v>95.2433725646046</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0078835843106085</v>
+        <v>-0.0106580876290864</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.0116664661793318</v>
+        <v>-0.00228713123043323</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0078525903611022</v>
+        <v>-0.0106014914605636</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>0.978886144610901</v>
+        <v>0.981657568491742</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>0.989435555110766</v>
+        <v>0.983579909791457</v>
       </c>
     </row>
     <row r="77">
@@ -5923,80 +5923,106 @@
         <v>106.453</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.01967576917357</v>
+        <v>1.01167309323326</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>0.44890997366091</v>
+        <v>0.0241131489806348</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>100.393094545403</v>
+        <v>99.5212629957377</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>97.009487075822</v>
+        <v>97.2550039077586</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>97.0926530864779</v>
+        <v>97.3512233946611</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>104.39887189462</v>
+        <v>105.224702240307</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>102.191327949732</v>
+        <v>99.658790875944</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>102.191327949732</v>
+        <v>99.658790875944</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>102.191327949732</v>
+        <v>99.658790875944</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>0.0667414413973424</v>
+        <v>0.0453168280768061</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>0.0966409850753069</v>
+        <v>0.0626529763231667</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>0.0690190383694202</v>
+        <v>0.0463593234095565</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.01791192325001</v>
+        <v>1.00138189444212</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.05341581560842</v>
+        <v>1.02471633203023</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="n">
+        <v>101.607</v>
+      </c>
       <c r="C78" s="3" t="n">
-        <v>101.208403846438</v>
+        <v>101.607</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>113.480917930405</v>
+        <v>101.607</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>90.2631137987933</v>
+        <v>101.607</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.00495774959793</v>
-      </c>
-      <c r="G78" s="7"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="12"/>
-      <c r="M78" s="13"/>
+        <v>1.00778273552543</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>101.763227397174</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>97.67858716306</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>97.9606698277105</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>100.822326497809</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <v>100.822326497809</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>100.822326497809</v>
+      </c>
       <c r="N78" s="14" t="n">
-        <v>100.709113280563</v>
-      </c>
-      <c r="O78" s="15"/>
-      <c r="P78" s="16"/>
-      <c r="Q78" s="17"/>
-      <c r="R78" s="18"/>
-      <c r="S78" s="19"/>
+        <v>100.822326497809</v>
+      </c>
+      <c r="O78" s="15" t="n">
+        <v>0.0116075638564973</v>
+      </c>
+      <c r="P78" s="16" t="n">
+        <v>0.090985824435226</v>
+      </c>
+      <c r="Q78" s="17" t="n">
+        <v>0.0116751930425623</v>
+      </c>
+      <c r="R78" s="18" t="n">
+        <v>0.990754018682085</v>
+      </c>
+      <c r="S78" s="19" t="n">
+        <v>1.03218452913842</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
@@ -6004,16 +6030,16 @@
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
-        <v>98.8813631784681</v>
+        <v>99.0773195061591</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>112.447197012806</v>
+        <v>110.990191961245</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>86.9521361472322</v>
+        <v>88.4430873311146</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.970826101468984</v>
+        <v>0.972249896731369</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -6023,7 +6049,7 @@
       <c r="L79" s="12"/>
       <c r="M79" s="13"/>
       <c r="N79" s="14" t="n">
-        <v>101.852806624016</v>
+        <v>101.90519931064</v>
       </c>
       <c r="O79" s="15"/>
       <c r="P79" s="16"/>
@@ -6037,16 +6063,16 @@
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3" t="n">
-        <v>99.2357255735799</v>
+        <v>99.3361898853688</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>113.224820032587</v>
+        <v>112.854861117298</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>86.9750044847108</v>
+        <v>87.4368948155975</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>1.00420997478367</v>
+        <v>1.00841615830084</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
@@ -6056,7 +6082,7 @@
       <c r="L80" s="12"/>
       <c r="M80" s="13"/>
       <c r="N80" s="14" t="n">
-        <v>98.8196971404885</v>
+        <v>98.507138216377</v>
       </c>
       <c r="O80" s="15"/>
       <c r="P80" s="16"/>
@@ -6070,16 +6096,16 @@
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="3" t="n">
-        <v>99.5913579017007</v>
+        <v>99.6937948377671</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>114.009261884485</v>
+        <v>113.633682227423</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>86.9967790753179</v>
+        <v>87.4639678512177</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.02154033754046</v>
+        <v>1.01249610314397</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
@@ -6089,7 +6115,7 @@
       <c r="L81" s="12"/>
       <c r="M81" s="13"/>
       <c r="N81" s="14" t="n">
-        <v>97.491361076827</v>
+        <v>98.4633862078097</v>
       </c>
       <c r="O81" s="15"/>
       <c r="P81" s="16"/>
@@ -6102,10 +6128,18 @@
         <v>134</v>
       </c>
       <c r="B82" s="2"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
+      <c r="C82" s="3" t="n">
+        <v>100.052687148802</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>114.419171985618</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>87.4900598560038</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>1.00600077757332</v>
+      </c>
       <c r="G82" s="7"/>
       <c r="H82" s="8"/>
       <c r="I82" s="9"/>
@@ -6113,7 +6147,9 @@
       <c r="K82" s="11"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13"/>
-      <c r="N82" s="14"/>
+      <c r="N82" s="14" t="n">
+        <v>99.4558745671644</v>
+      </c>
       <c r="O82" s="15"/>
       <c r="P82" s="16"/>
       <c r="Q82" s="17"/>
@@ -6611,7 +6647,7 @@
         <v>171</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0513481891249785</v>
+        <v>-0.0466424851109004</v>
       </c>
     </row>
     <row r="6">
@@ -6619,7 +6655,7 @@
         <v>172</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0510780830098253</v>
+        <v>0.0434573223693458</v>
       </c>
     </row>
     <row r="7">
@@ -6627,7 +6663,7 @@
         <v>173</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.00544327674559669</v>
+        <v>-0.00512937984246431</v>
       </c>
     </row>
     <row r="8">
@@ -6635,7 +6671,7 @@
         <v>174</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.000659657951635425</v>
+        <v>0.0144610680506305</v>
       </c>
     </row>
     <row r="9">
@@ -6643,7 +6679,7 @@
         <v>175</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>-0.010919642501838</v>
+        <v>-0.0237366653853741</v>
       </c>
     </row>
     <row r="10">
@@ -6651,7 +6687,7 @@
         <v>176</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.0662343912007149</v>
+        <v>0.0746937342624868</v>
       </c>
     </row>
     <row r="11">
@@ -6659,7 +6695,7 @@
         <v>177</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.0261872563151287</v>
+        <v>0.0166078117590781</v>
       </c>
     </row>
     <row r="12">
@@ -6667,7 +6703,7 @@
         <v>178</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.0104029622417957</v>
+        <v>-0.0178616543036067</v>
       </c>
     </row>
     <row r="13">
@@ -6675,7 +6711,7 @@
         <v>179</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0623526222207706</v>
+        <v>0.0600035634647469</v>
       </c>
     </row>
     <row r="14">
